--- a/bcpindustrias.xlsx
+++ b/bcpindustrias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SistemaGestionyelave\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C71E85C-7F86-4A66-8C14-451E066E0FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF563468-1479-4A49-94EF-E045EDBF1D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8704B657-9C0E-49DF-B167-FE76DDFEDB25}"/>
   </bookViews>
@@ -5515,12 +5515,12 @@
     </font>
     <font>
       <sz val="8"/>
-      <color rgb="FF64748B"/>
+      <color theme="0"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5530,6 +5530,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5548,9 +5554,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5892,4265 +5898,4265 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>45660</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>354.6</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>1188</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>1399</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>1610</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>45663</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>275.2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>1189</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>1400</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>1611</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>45664</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>11.6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>1401</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>1612</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>45664</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>38.9</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>1191</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>1402</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="2" t="s">
         <v>1613</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>45664</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>387</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>1192</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>1403</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="2" t="s">
         <v>1614</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>45666</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>193.6</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>1193</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="2" t="s">
         <v>1404</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="2" t="s">
         <v>1615</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>45667</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>283</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>1194</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="2" t="s">
         <v>1405</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="2" t="s">
         <v>1616</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>45671</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>92.5</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>1195</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="2" t="s">
         <v>1406</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="2" t="s">
         <v>1617</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>45672</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>1057</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>467.98</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="2" t="s">
         <v>1407</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="2" t="s">
         <v>1618</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>45672</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>10299.24</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>1197</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="2" t="s">
         <v>1408</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="2" t="s">
         <v>1619</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>45674</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>358.17</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>1198</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="2" t="s">
         <v>1409</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="2" t="s">
         <v>1620</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>45674</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>430</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>1199</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="2" t="s">
         <v>1410</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="K13" s="2" t="s">
         <v>1621</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>45677</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>414.82</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>1200</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="2" t="s">
         <v>1411</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" s="2" t="s">
         <v>1622</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>45677</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>1062</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <v>829.64</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="2" t="s">
         <v>1201</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="2" t="s">
         <v>1412</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="K15" s="2" t="s">
         <v>1623</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>45678</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>156.11000000000001</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" s="2" t="s">
         <v>1413</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="K16" s="2" t="s">
         <v>1624</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>45678</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <v>163.6</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="J17" s="2" t="s">
         <v>1414</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="K17" s="2" t="s">
         <v>1625</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>45680</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <v>68.8</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="J18" s="2" t="s">
         <v>1415</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="K18" s="2" t="s">
         <v>1626</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>45680</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <v>187.1</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="2" t="s">
         <v>1205</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="J19" s="2" t="s">
         <v>1416</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="K19" s="2" t="s">
         <v>1627</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>45680</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="2">
         <v>5000</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="2" t="s">
         <v>1417</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="K20" s="2" t="s">
         <v>1628</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>45681</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="2">
         <v>265</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="2" t="s">
         <v>1207</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="2" t="s">
         <v>1418</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="K21" s="2" t="s">
         <v>1629</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>45684</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="2">
         <v>118.8</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="2" t="s">
         <v>1208</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="2" t="s">
         <v>1419</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="K22" s="2" t="s">
         <v>1630</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>45686</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="2">
         <v>121.72</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="2" t="s">
         <v>1209</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J23" s="2" t="s">
         <v>1420</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="K23" s="2" t="s">
         <v>1631</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="A24" s="1">
         <v>45686</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="2">
         <v>950.41</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="2" t="s">
         <v>1210</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="J24" s="2" t="s">
         <v>1421</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="K24" s="2" t="s">
         <v>1632</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="A25" s="1">
         <v>45687</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="2">
         <v>843.1</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="J25" s="2" t="s">
         <v>1422</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="K25" s="2" t="s">
         <v>1633</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="A26" s="1">
         <v>45687</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="2">
         <v>13343.15</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="2" t="s">
         <v>1212</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="J26" s="2" t="s">
         <v>1423</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="K26" s="2" t="s">
         <v>1634</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>45688</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="2">
         <v>28.5</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="2" t="s">
         <v>1213</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="J27" s="2" t="s">
         <v>1424</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="K27" s="2" t="s">
         <v>1635</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="A28" s="1">
         <v>45688</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="2">
         <v>29.7</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="J28" s="2" t="s">
         <v>1425</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="K28" s="2" t="s">
         <v>1636</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="A29" s="1">
         <v>45688</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="2">
         <v>427</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="J29" s="2" t="s">
         <v>1426</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="K29" s="2" t="s">
         <v>1637</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="A30" s="1">
         <v>45691</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="2">
         <v>577.73</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="2" t="s">
         <v>1216</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="J30" s="2" t="s">
         <v>1427</v>
       </c>
-      <c r="K30" s="3" t="s">
+      <c r="K30" s="2" t="s">
         <v>1638</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="A31" s="1">
         <v>45693</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="2">
         <v>488.6</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="2" t="s">
         <v>1217</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J31" s="2" t="s">
         <v>1428</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="K31" s="2" t="s">
         <v>1639</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="A32" s="1">
         <v>45694</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="2">
         <v>93.2</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="J32" s="2" t="s">
         <v>1429</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="K32" s="2" t="s">
         <v>1640</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="A33" s="1">
         <v>45698</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="2">
         <v>488.9</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="2" t="s">
         <v>1219</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="J33" s="2" t="s">
         <v>1430</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="K33" s="2" t="s">
         <v>1641</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="A34" s="1">
         <v>45699</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="2">
         <v>466</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="J34" s="2" t="s">
         <v>1431</v>
       </c>
-      <c r="K34" s="3" t="s">
+      <c r="K34" s="2" t="s">
         <v>1642</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="A35" s="1">
         <v>45701</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="2">
         <v>75.8</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J35" s="2" t="s">
         <v>1432</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="K35" s="2" t="s">
         <v>1643</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="A36" s="1">
         <v>45701</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="2">
         <v>113.1</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="2" t="s">
         <v>1222</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="J36" s="2" t="s">
         <v>1433</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="K36" s="2" t="s">
         <v>1644</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="A37" s="1">
         <v>45701</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="2">
         <v>202.4</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="J37" s="2" t="s">
         <v>1434</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="K37" s="2" t="s">
         <v>1645</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="A38" s="1">
         <v>45701</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="2">
         <v>10267.84</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="2" t="s">
         <v>1224</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="J38" s="2" t="s">
         <v>1435</v>
       </c>
-      <c r="K38" s="3" t="s">
+      <c r="K38" s="2" t="s">
         <v>1646</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="A39" s="1">
         <v>45705</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="2">
         <v>260</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="J39" s="2" t="s">
         <v>1436</v>
       </c>
-      <c r="K39" s="3" t="s">
+      <c r="K39" s="2" t="s">
         <v>1647</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="A40" s="1">
         <v>45706</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>1073</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="2">
         <v>99.2</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="J40" s="2" t="s">
         <v>1437</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="K40" s="2" t="s">
         <v>1648</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="A41" s="1">
         <v>45706</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="2">
         <v>182</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="2" t="s">
         <v>1227</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="J41" s="2" t="s">
         <v>1438</v>
       </c>
-      <c r="K41" s="3" t="s">
+      <c r="K41" s="2" t="s">
         <v>1649</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="A42" s="1">
         <v>45706</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>1074</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="2">
         <v>489.99</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F42" s="2" t="s">
         <v>1228</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="J42" s="2" t="s">
         <v>1439</v>
       </c>
-      <c r="K42" s="3" t="s">
+      <c r="K42" s="2" t="s">
         <v>1650</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="A43" s="1">
         <v>45706</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="2">
         <v>771.72</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="J43" s="2" t="s">
         <v>1440</v>
       </c>
-      <c r="K43" s="3" t="s">
+      <c r="K43" s="2" t="s">
         <v>1651</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="A44" s="1">
         <v>45708</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="2">
         <v>414.82</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="2" t="s">
         <v>1230</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="J44" s="2" t="s">
         <v>1441</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="K44" s="2" t="s">
         <v>1652</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="A45" s="1">
         <v>45708</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>1077</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="2">
         <v>1386.94</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="2" t="s">
         <v>1231</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="J45" s="2" t="s">
         <v>1442</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="K45" s="2" t="s">
         <v>1653</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="A46" s="1">
         <v>45708</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="2">
         <v>1450</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="2" t="s">
         <v>1232</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="J46" s="2" t="s">
         <v>1443</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="K46" s="2" t="s">
         <v>1654</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="A47" s="1">
         <v>45709</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>1078</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="2">
         <v>99.6</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="2" t="s">
         <v>1233</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="J47" s="2" t="s">
         <v>1444</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="K47" s="2" t="s">
         <v>1655</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="A48" s="1">
         <v>45712</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="2">
         <v>1894.39</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="J48" s="2" t="s">
         <v>1445</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="K48" s="2" t="s">
         <v>1656</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="A49" s="1">
         <v>45713</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="2">
         <v>123.1</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="J49" s="2" t="s">
         <v>1446</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="K49" s="2" t="s">
         <v>1657</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="A50" s="1">
         <v>45713</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="2">
         <v>315.3</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="2" t="s">
         <v>1236</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="J50" s="2" t="s">
         <v>1447</v>
       </c>
-      <c r="K50" s="3" t="s">
+      <c r="K50" s="2" t="s">
         <v>1658</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+      <c r="A51" s="1">
         <v>45714</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="2">
         <v>153.69999999999999</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="2" t="s">
         <v>1237</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="J51" s="2" t="s">
         <v>1448</v>
       </c>
-      <c r="K51" s="3" t="s">
+      <c r="K51" s="2" t="s">
         <v>1659</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="A52" s="1">
         <v>45716</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>1081</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="2">
         <v>142</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="2" t="s">
         <v>1238</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="J52" s="2" t="s">
         <v>1449</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="K52" s="2" t="s">
         <v>1660</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+      <c r="A53" s="1">
         <v>45716</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>1082</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="2">
         <v>13146.96</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="2" t="s">
         <v>1239</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="J53" s="2" t="s">
         <v>1450</v>
       </c>
-      <c r="K53" s="3" t="s">
+      <c r="K53" s="2" t="s">
         <v>1661</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+      <c r="A54" s="1">
         <v>45721</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="2">
         <v>84.2</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="2" t="s">
         <v>1240</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="J54" s="2" t="s">
         <v>1451</v>
       </c>
-      <c r="K54" s="3" t="s">
+      <c r="K54" s="2" t="s">
         <v>1662</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+      <c r="A55" s="1">
         <v>45722</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="2">
         <v>231.8</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="2" t="s">
         <v>1241</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="J55" s="2" t="s">
         <v>1452</v>
       </c>
-      <c r="K55" s="3" t="s">
+      <c r="K55" s="2" t="s">
         <v>1663</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+      <c r="A56" s="1">
         <v>45723</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="2">
         <v>6.61</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="F56" s="2" t="s">
         <v>1242</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="J56" s="2" t="s">
         <v>1453</v>
       </c>
-      <c r="K56" s="3" t="s">
+      <c r="K56" s="2" t="s">
         <v>1664</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="A57" s="1">
         <v>45723</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>1084</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="2">
         <v>125</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="J57" s="2" t="s">
         <v>1454</v>
       </c>
-      <c r="K57" s="3" t="s">
+      <c r="K57" s="2" t="s">
         <v>1665</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="A58" s="1">
         <v>45723</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>1074</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="2">
         <v>489.99</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F58" s="2" t="s">
         <v>1244</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="J58" s="2" t="s">
         <v>1455</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="K58" s="2" t="s">
         <v>1666</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+      <c r="A59" s="1">
         <v>45723</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="2">
         <v>3000</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="F59" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="J59" s="2" t="s">
         <v>1456</v>
       </c>
-      <c r="K59" s="3" t="s">
+      <c r="K59" s="2" t="s">
         <v>1667</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+      <c r="A60" s="1">
         <v>45726</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="2">
         <v>200</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="F60" s="2" t="s">
         <v>1246</v>
       </c>
-      <c r="J60" s="3" t="s">
+      <c r="J60" s="2" t="s">
         <v>1457</v>
       </c>
-      <c r="K60" s="3" t="s">
+      <c r="K60" s="2" t="s">
         <v>1668</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+      <c r="A61" s="1">
         <v>45726</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="2">
         <v>1032.95</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="F61" s="2" t="s">
         <v>1247</v>
       </c>
-      <c r="J61" s="3" t="s">
+      <c r="J61" s="2" t="s">
         <v>1458</v>
       </c>
-      <c r="K61" s="3" t="s">
+      <c r="K61" s="2" t="s">
         <v>1669</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+      <c r="A62" s="1">
         <v>45727</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="2">
         <v>43.6</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F62" s="2" t="s">
         <v>1248</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="J62" s="2" t="s">
         <v>1459</v>
       </c>
-      <c r="K62" s="3" t="s">
+      <c r="K62" s="2" t="s">
         <v>1670</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+      <c r="A63" s="1">
         <v>45729</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="2">
         <v>300</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="F63" s="2" t="s">
         <v>1249</v>
       </c>
-      <c r="J63" s="3" t="s">
+      <c r="J63" s="2" t="s">
         <v>1460</v>
       </c>
-      <c r="K63" s="3" t="s">
+      <c r="K63" s="2" t="s">
         <v>1671</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+      <c r="A64" s="1">
         <v>45729</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2" t="s">
         <v>1086</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="2">
         <v>1167.6199999999999</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F64" s="2" t="s">
         <v>1250</v>
       </c>
-      <c r="J64" s="3" t="s">
+      <c r="J64" s="2" t="s">
         <v>1461</v>
       </c>
-      <c r="K64" s="3" t="s">
+      <c r="K64" s="2" t="s">
         <v>1672</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+      <c r="A65" s="1">
         <v>45729</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65" s="2">
         <v>9563.7999999999993</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="J65" s="2" t="s">
         <v>1462</v>
       </c>
-      <c r="K65" s="3" t="s">
+      <c r="K65" s="2" t="s">
         <v>1673</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="A66" s="1">
         <v>45730</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66" s="2">
         <v>237.6</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="2" t="s">
         <v>1252</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="J66" s="2" t="s">
         <v>1463</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="K66" s="2" t="s">
         <v>1674</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="A67" s="1">
         <v>45730</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="2">
         <v>286</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" s="2" t="s">
         <v>1253</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="J67" s="2" t="s">
         <v>1464</v>
       </c>
-      <c r="K67" s="3" t="s">
+      <c r="K67" s="2" t="s">
         <v>1675</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="A68" s="1">
         <v>45735</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="2">
         <v>238.4</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" s="2" t="s">
         <v>1254</v>
       </c>
-      <c r="J68" s="3" t="s">
+      <c r="J68" s="2" t="s">
         <v>1465</v>
       </c>
-      <c r="K68" s="3" t="s">
+      <c r="K68" s="2" t="s">
         <v>1676</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+      <c r="A69" s="1">
         <v>45736</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69" s="2">
         <v>99.2</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="F69" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="J69" s="3" t="s">
+      <c r="J69" s="2" t="s">
         <v>1466</v>
       </c>
-      <c r="K69" s="3" t="s">
+      <c r="K69" s="2" t="s">
         <v>1677</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="A70" s="1">
         <v>45736</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="2">
         <v>471.92</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F70" s="2" t="s">
         <v>1256</v>
       </c>
-      <c r="J70" s="3" t="s">
+      <c r="J70" s="2" t="s">
         <v>1467</v>
       </c>
-      <c r="K70" s="3" t="s">
+      <c r="K70" s="2" t="s">
         <v>1678</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
+      <c r="A71" s="1">
         <v>45736</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="2">
         <v>669.57</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F71" s="2" t="s">
         <v>1257</v>
       </c>
-      <c r="J71" s="3" t="s">
+      <c r="J71" s="2" t="s">
         <v>1468</v>
       </c>
-      <c r="K71" s="3" t="s">
+      <c r="K71" s="2" t="s">
         <v>1679</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="A72" s="1">
         <v>45736</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="2">
         <v>3000</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F72" s="2" t="s">
         <v>1258</v>
       </c>
-      <c r="J72" s="3" t="s">
+      <c r="J72" s="2" t="s">
         <v>1469</v>
       </c>
-      <c r="K72" s="3" t="s">
+      <c r="K72" s="2" t="s">
         <v>1680</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+      <c r="A73" s="1">
         <v>45737</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="C73" s="3">
+      <c r="C73" s="2">
         <v>1894.81</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="2" t="s">
         <v>1259</v>
       </c>
-      <c r="J73" s="3" t="s">
+      <c r="J73" s="2" t="s">
         <v>1470</v>
       </c>
-      <c r="K73" s="3" t="s">
+      <c r="K73" s="2" t="s">
         <v>1681</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="A74" s="1">
         <v>45739</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74" s="2">
         <v>177.6</v>
       </c>
-      <c r="F74" s="3" t="s">
+      <c r="F74" s="2" t="s">
         <v>1260</v>
       </c>
-      <c r="J74" s="3" t="s">
+      <c r="J74" s="2" t="s">
         <v>1471</v>
       </c>
-      <c r="K74" s="3" t="s">
+      <c r="K74" s="2" t="s">
         <v>1682</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+      <c r="A75" s="1">
         <v>45740</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C75" s="3">
+      <c r="C75" s="2">
         <v>54.8</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="F75" s="2" t="s">
         <v>1261</v>
       </c>
-      <c r="J75" s="3" t="s">
+      <c r="J75" s="2" t="s">
         <v>1472</v>
       </c>
-      <c r="K75" s="3" t="s">
+      <c r="K75" s="2" t="s">
         <v>1683</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+      <c r="A76" s="1">
         <v>45741</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C76" s="2">
         <v>140.19999999999999</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F76" s="2" t="s">
         <v>1262</v>
       </c>
-      <c r="J76" s="3" t="s">
+      <c r="J76" s="2" t="s">
         <v>1473</v>
       </c>
-      <c r="K76" s="3" t="s">
+      <c r="K76" s="2" t="s">
         <v>1684</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+      <c r="A77" s="1">
         <v>45742</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="C77" s="3">
+      <c r="C77" s="2">
         <v>491.2</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="J77" s="3" t="s">
+      <c r="J77" s="2" t="s">
         <v>1474</v>
       </c>
-      <c r="K77" s="3" t="s">
+      <c r="K77" s="2" t="s">
         <v>1685</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+      <c r="A78" s="1">
         <v>45743</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="2" t="s">
         <v>1094</v>
       </c>
-      <c r="C78" s="3">
+      <c r="C78" s="2">
         <v>2996.84</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="2" t="s">
         <v>1264</v>
       </c>
-      <c r="J78" s="3" t="s">
+      <c r="J78" s="2" t="s">
         <v>1475</v>
       </c>
-      <c r="K78" s="3" t="s">
+      <c r="K78" s="2" t="s">
         <v>1686</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="A79" s="1">
         <v>45747</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="2" t="s">
         <v>1095</v>
       </c>
-      <c r="C79" s="3">
+      <c r="C79" s="2">
         <v>10590.11</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="2" t="s">
         <v>1265</v>
       </c>
-      <c r="J79" s="3" t="s">
+      <c r="J79" s="2" t="s">
         <v>1476</v>
       </c>
-      <c r="K79" s="3" t="s">
+      <c r="K79" s="2" t="s">
         <v>1687</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="A80" s="1">
         <v>45751</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="C80" s="3">
+      <c r="C80" s="2">
         <v>44</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="2" t="s">
         <v>1266</v>
       </c>
-      <c r="J80" s="3" t="s">
+      <c r="J80" s="2" t="s">
         <v>1477</v>
       </c>
-      <c r="K80" s="3" t="s">
+      <c r="K80" s="2" t="s">
         <v>1688</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+      <c r="A81" s="1">
         <v>45757</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="2" t="s">
         <v>1096</v>
       </c>
-      <c r="C81" s="3">
+      <c r="C81" s="2">
         <v>214.4</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="2" t="s">
         <v>1267</v>
       </c>
-      <c r="J81" s="3" t="s">
+      <c r="J81" s="2" t="s">
         <v>1478</v>
       </c>
-      <c r="K81" s="3" t="s">
+      <c r="K81" s="2" t="s">
         <v>1689</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+      <c r="A82" s="1">
         <v>45757</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="C82" s="3">
+      <c r="C82" s="2">
         <v>260.02</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="2" t="s">
         <v>1268</v>
       </c>
-      <c r="J82" s="3" t="s">
+      <c r="J82" s="2" t="s">
         <v>1479</v>
       </c>
-      <c r="K82" s="3" t="s">
+      <c r="K82" s="2" t="s">
         <v>1690</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
+      <c r="A83" s="1">
         <v>45757</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="C83" s="3">
+      <c r="C83" s="2">
         <v>390.04</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="2" t="s">
         <v>1269</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="J83" s="2" t="s">
         <v>1480</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="K83" s="2" t="s">
         <v>1691</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+      <c r="A84" s="1">
         <v>45757</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="C84" s="3">
+      <c r="C84" s="2">
         <v>390.04</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="2" t="s">
         <v>1270</v>
       </c>
-      <c r="J84" s="3" t="s">
+      <c r="J84" s="2" t="s">
         <v>1481</v>
       </c>
-      <c r="K84" s="3" t="s">
+      <c r="K84" s="2" t="s">
         <v>1692</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+      <c r="A85" s="1">
         <v>45758</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C85" s="3">
+      <c r="C85" s="2">
         <v>124.8</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="2" t="s">
         <v>1271</v>
       </c>
-      <c r="J85" s="3" t="s">
+      <c r="J85" s="2" t="s">
         <v>1482</v>
       </c>
-      <c r="K85" s="3" t="s">
+      <c r="K85" s="2" t="s">
         <v>1693</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
+      <c r="A86" s="1">
         <v>45762</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="C86" s="3">
+      <c r="C86" s="2">
         <v>296.3</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="2" t="s">
         <v>1272</v>
       </c>
-      <c r="J86" s="3" t="s">
+      <c r="J86" s="2" t="s">
         <v>1483</v>
       </c>
-      <c r="K86" s="3" t="s">
+      <c r="K86" s="2" t="s">
         <v>1694</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+      <c r="A87" s="1">
         <v>45762</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="2" t="s">
         <v>1101</v>
       </c>
-      <c r="C87" s="3">
+      <c r="C87" s="2">
         <v>9267.5</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="2" t="s">
         <v>1273</v>
       </c>
-      <c r="J87" s="3" t="s">
+      <c r="J87" s="2" t="s">
         <v>1484</v>
       </c>
-      <c r="K87" s="3" t="s">
+      <c r="K87" s="2" t="s">
         <v>1695</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
+      <c r="A88" s="1">
         <v>45763</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="2" t="s">
         <v>1081</v>
       </c>
-      <c r="C88" s="3">
+      <c r="C88" s="2">
         <v>183.8</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="F88" s="2" t="s">
         <v>1274</v>
       </c>
-      <c r="J88" s="3" t="s">
+      <c r="J88" s="2" t="s">
         <v>1485</v>
       </c>
-      <c r="K88" s="3" t="s">
+      <c r="K88" s="2" t="s">
         <v>1696</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+      <c r="A89" s="1">
         <v>45768</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C89" s="3">
+      <c r="C89" s="2">
         <v>232</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="F89" s="2" t="s">
         <v>1275</v>
       </c>
-      <c r="J89" s="3" t="s">
+      <c r="J89" s="2" t="s">
         <v>1486</v>
       </c>
-      <c r="K89" s="3" t="s">
+      <c r="K89" s="2" t="s">
         <v>1697</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+      <c r="A90" s="1">
         <v>45769</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="C90" s="3">
+      <c r="C90" s="2">
         <v>212.21</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="2" t="s">
         <v>1276</v>
       </c>
-      <c r="J90" s="3" t="s">
+      <c r="J90" s="2" t="s">
         <v>1487</v>
       </c>
-      <c r="K90" s="3" t="s">
+      <c r="K90" s="2" t="s">
         <v>1698</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+      <c r="A91" s="1">
         <v>45769</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>1103</v>
       </c>
-      <c r="C91" s="3">
+      <c r="C91" s="2">
         <v>312.02999999999997</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F91" s="2" t="s">
         <v>1277</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="J91" s="2" t="s">
         <v>1488</v>
       </c>
-      <c r="K91" s="3" t="s">
+      <c r="K91" s="2" t="s">
         <v>1699</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+      <c r="A92" s="1">
         <v>45769</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="C92" s="3">
+      <c r="C92" s="2">
         <v>1116.6099999999999</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="F92" s="2" t="s">
         <v>1278</v>
       </c>
-      <c r="J92" s="3" t="s">
+      <c r="J92" s="2" t="s">
         <v>1489</v>
       </c>
-      <c r="K92" s="3" t="s">
+      <c r="K92" s="2" t="s">
         <v>1700</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
+      <c r="A93" s="1">
         <v>45769</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="C93" s="3">
+      <c r="C93" s="2">
         <v>2259.9</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="2" t="s">
         <v>1279</v>
       </c>
-      <c r="J93" s="3" t="s">
+      <c r="J93" s="2" t="s">
         <v>1490</v>
       </c>
-      <c r="K93" s="3" t="s">
+      <c r="K93" s="2" t="s">
         <v>1701</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+      <c r="A94" s="1">
         <v>45769</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="C94" s="3">
+      <c r="C94" s="2">
         <v>3000</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="2" t="s">
         <v>1280</v>
       </c>
-      <c r="J94" s="3" t="s">
+      <c r="J94" s="2" t="s">
         <v>1491</v>
       </c>
-      <c r="K94" s="3" t="s">
+      <c r="K94" s="2" t="s">
         <v>1702</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
+      <c r="A95" s="1">
         <v>45775</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="C95" s="3">
+      <c r="C95" s="2">
         <v>7.6</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="F95" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="J95" s="3" t="s">
+      <c r="J95" s="2" t="s">
         <v>1492</v>
       </c>
-      <c r="K95" s="3" t="s">
+      <c r="K95" s="2" t="s">
         <v>1703</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
+      <c r="A96" s="1">
         <v>45775</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C96" s="3">
+      <c r="C96" s="2">
         <v>321.2</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F96" s="2" t="s">
         <v>1282</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="J96" s="2" t="s">
         <v>1493</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="K96" s="2" t="s">
         <v>1704</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
+      <c r="A97" s="1">
         <v>45775</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="C97" s="3">
+      <c r="C97" s="2">
         <v>391.8</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F97" s="2" t="s">
         <v>1283</v>
       </c>
-      <c r="J97" s="3" t="s">
+      <c r="J97" s="2" t="s">
         <v>1494</v>
       </c>
-      <c r="K97" s="3" t="s">
+      <c r="K97" s="2" t="s">
         <v>1705</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
+      <c r="A98" s="1">
         <v>45776</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="C98" s="3">
+      <c r="C98" s="2">
         <v>12009.39</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="F98" s="2" t="s">
         <v>1284</v>
       </c>
-      <c r="J98" s="3" t="s">
+      <c r="J98" s="2" t="s">
         <v>1495</v>
       </c>
-      <c r="K98" s="3" t="s">
+      <c r="K98" s="2" t="s">
         <v>1706</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
+      <c r="A99" s="1">
         <v>45777</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C99" s="3">
+      <c r="C99" s="2">
         <v>34.700000000000003</v>
       </c>
-      <c r="F99" s="3" t="s">
+      <c r="F99" s="2" t="s">
         <v>1285</v>
       </c>
-      <c r="J99" s="3" t="s">
+      <c r="J99" s="2" t="s">
         <v>1496</v>
       </c>
-      <c r="K99" s="3" t="s">
+      <c r="K99" s="2" t="s">
         <v>1707</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
+      <c r="A100" s="1">
         <v>45777</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C100" s="3">
+      <c r="C100" s="2">
         <v>35</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="F100" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="J100" s="3" t="s">
+      <c r="J100" s="2" t="s">
         <v>1497</v>
       </c>
-      <c r="K100" s="3" t="s">
+      <c r="K100" s="2" t="s">
         <v>1708</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
+      <c r="A101" s="1">
         <v>45785</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="C101" s="3">
+      <c r="C101" s="2">
         <v>2000</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="F101" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="J101" s="2" t="s">
         <v>1498</v>
       </c>
-      <c r="K101" s="3" t="s">
+      <c r="K101" s="2" t="s">
         <v>1709</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
+      <c r="A102" s="1">
         <v>45786</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C102" s="3">
+      <c r="C102" s="2">
         <v>125</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="F102" s="2" t="s">
         <v>1288</v>
       </c>
-      <c r="J102" s="3" t="s">
+      <c r="J102" s="2" t="s">
         <v>1499</v>
       </c>
-      <c r="K102" s="3" t="s">
+      <c r="K102" s="2" t="s">
         <v>1710</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
+      <c r="A103" s="1">
         <v>45786</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="C103" s="3">
+      <c r="C103" s="2">
         <v>2816.4</v>
       </c>
-      <c r="F103" s="3" t="s">
+      <c r="F103" s="2" t="s">
         <v>1289</v>
       </c>
-      <c r="J103" s="3" t="s">
+      <c r="J103" s="2" t="s">
         <v>1500</v>
       </c>
-      <c r="K103" s="3" t="s">
+      <c r="K103" s="2" t="s">
         <v>1711</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
+      <c r="A104" s="1">
         <v>45789</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="C104" s="3">
+      <c r="C104" s="2">
         <v>140.69999999999999</v>
       </c>
-      <c r="F104" s="3" t="s">
+      <c r="F104" s="2" t="s">
         <v>1290</v>
       </c>
-      <c r="J104" s="3" t="s">
+      <c r="J104" s="2" t="s">
         <v>1501</v>
       </c>
-      <c r="K104" s="3" t="s">
+      <c r="K104" s="2" t="s">
         <v>1712</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
+      <c r="A105" s="1">
         <v>45790</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="C105" s="3">
+      <c r="C105" s="2">
         <v>9688.4</v>
       </c>
-      <c r="F105" s="3" t="s">
+      <c r="F105" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="J105" s="3" t="s">
+      <c r="J105" s="2" t="s">
         <v>1502</v>
       </c>
-      <c r="K105" s="3" t="s">
+      <c r="K105" s="2" t="s">
         <v>1713</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
+      <c r="A106" s="1">
         <v>45792</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="C106" s="3">
+      <c r="C106" s="2">
         <v>3000</v>
       </c>
-      <c r="F106" s="3" t="s">
+      <c r="F106" s="2" t="s">
         <v>1292</v>
       </c>
-      <c r="J106" s="3" t="s">
+      <c r="J106" s="2" t="s">
         <v>1503</v>
       </c>
-      <c r="K106" s="3" t="s">
+      <c r="K106" s="2" t="s">
         <v>1714</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
+      <c r="A107" s="1">
         <v>45793</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="C107" s="3">
+      <c r="C107" s="2">
         <v>313.89999999999998</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="F107" s="2" t="s">
         <v>1293</v>
       </c>
-      <c r="J107" s="3" t="s">
+      <c r="J107" s="2" t="s">
         <v>1504</v>
       </c>
-      <c r="K107" s="3" t="s">
+      <c r="K107" s="2" t="s">
         <v>1715</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
+      <c r="A108" s="1">
         <v>45796</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="C108" s="3">
+      <c r="C108" s="2">
         <v>0.33</v>
       </c>
-      <c r="F108" s="3" t="s">
+      <c r="F108" s="2" t="s">
         <v>1294</v>
       </c>
-      <c r="J108" s="3" t="s">
+      <c r="J108" s="2" t="s">
         <v>1505</v>
       </c>
-      <c r="K108" s="3" t="s">
+      <c r="K108" s="2" t="s">
         <v>1716</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
+      <c r="A109" s="1">
         <v>45796</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C109" s="3">
+      <c r="C109" s="2">
         <v>120</v>
       </c>
-      <c r="F109" s="3" t="s">
+      <c r="F109" s="2" t="s">
         <v>1295</v>
       </c>
-      <c r="J109" s="3" t="s">
+      <c r="J109" s="2" t="s">
         <v>1506</v>
       </c>
-      <c r="K109" s="3" t="s">
+      <c r="K109" s="2" t="s">
         <v>1717</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
+      <c r="A110" s="1">
         <v>45797</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="C110" s="3">
+      <c r="C110" s="2">
         <v>4800</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="F110" s="2" t="s">
         <v>1296</v>
       </c>
-      <c r="J110" s="3" t="s">
+      <c r="J110" s="2" t="s">
         <v>1507</v>
       </c>
-      <c r="K110" s="3" t="s">
+      <c r="K110" s="2" t="s">
         <v>1718</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
+      <c r="A111" s="1">
         <v>45799</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="C111" s="3">
+      <c r="C111" s="2">
         <v>1</v>
       </c>
-      <c r="F111" s="3" t="s">
+      <c r="F111" s="2" t="s">
         <v>1297</v>
       </c>
-      <c r="J111" s="3" t="s">
+      <c r="J111" s="2" t="s">
         <v>1508</v>
       </c>
-      <c r="K111" s="3" t="s">
+      <c r="K111" s="2" t="s">
         <v>1719</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
+      <c r="A112" s="1">
         <v>45799</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C112" s="3">
+      <c r="C112" s="2">
         <v>99.9</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F112" s="2" t="s">
         <v>1298</v>
       </c>
-      <c r="J112" s="3" t="s">
+      <c r="J112" s="2" t="s">
         <v>1509</v>
       </c>
-      <c r="K112" s="3" t="s">
+      <c r="K112" s="2" t="s">
         <v>1720</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
+      <c r="A113" s="1">
         <v>45799</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="2" t="s">
         <v>1112</v>
       </c>
-      <c r="C113" s="3">
+      <c r="C113" s="2">
         <v>2415.52</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="F113" s="2" t="s">
         <v>1299</v>
       </c>
-      <c r="J113" s="3" t="s">
+      <c r="J113" s="2" t="s">
         <v>1510</v>
       </c>
-      <c r="K113" s="3" t="s">
+      <c r="K113" s="2" t="s">
         <v>1721</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
+      <c r="A114" s="1">
         <v>45800</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="C114" s="3">
+      <c r="C114" s="2">
         <v>1000</v>
       </c>
-      <c r="F114" s="3" t="s">
+      <c r="F114" s="2" t="s">
         <v>1300</v>
       </c>
-      <c r="J114" s="3" t="s">
+      <c r="J114" s="2" t="s">
         <v>1511</v>
       </c>
-      <c r="K114" s="3" t="s">
+      <c r="K114" s="2" t="s">
         <v>1722</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
+      <c r="A115" s="1">
         <v>45803</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="C115" s="3">
+      <c r="C115" s="2">
         <v>27.75</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="F115" s="2" t="s">
         <v>1301</v>
       </c>
-      <c r="J115" s="3" t="s">
+      <c r="J115" s="2" t="s">
         <v>1512</v>
       </c>
-      <c r="K115" s="3" t="s">
+      <c r="K115" s="2" t="s">
         <v>1723</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" s="2">
+      <c r="A116" s="1">
         <v>45806</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="C116" s="3">
+      <c r="C116" s="2">
         <v>10885.11</v>
       </c>
-      <c r="F116" s="3" t="s">
+      <c r="F116" s="2" t="s">
         <v>1302</v>
       </c>
-      <c r="J116" s="3" t="s">
+      <c r="J116" s="2" t="s">
         <v>1513</v>
       </c>
-      <c r="K116" s="3" t="s">
+      <c r="K116" s="2" t="s">
         <v>1724</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
+      <c r="A117" s="1">
         <v>45814</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="C117" s="3">
+      <c r="C117" s="2">
         <v>1000</v>
       </c>
-      <c r="F117" s="3" t="s">
+      <c r="F117" s="2" t="s">
         <v>1303</v>
       </c>
-      <c r="J117" s="3" t="s">
+      <c r="J117" s="2" t="s">
         <v>1514</v>
       </c>
-      <c r="K117" s="3" t="s">
+      <c r="K117" s="2" t="s">
         <v>1725</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
+      <c r="A118" s="1">
         <v>45814</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="C118" s="3">
+      <c r="C118" s="2">
         <v>1480.84</v>
       </c>
-      <c r="F118" s="3" t="s">
+      <c r="F118" s="2" t="s">
         <v>1304</v>
       </c>
-      <c r="J118" s="3" t="s">
+      <c r="J118" s="2" t="s">
         <v>1515</v>
       </c>
-      <c r="K118" s="3" t="s">
+      <c r="K118" s="2" t="s">
         <v>1726</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
+      <c r="A119" s="1">
         <v>45821</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="C119" s="3">
+      <c r="C119" s="2">
         <v>11068.62</v>
       </c>
-      <c r="F119" s="3" t="s">
+      <c r="F119" s="2" t="s">
         <v>1305</v>
       </c>
-      <c r="J119" s="3" t="s">
+      <c r="J119" s="2" t="s">
         <v>1516</v>
       </c>
-      <c r="K119" s="3" t="s">
+      <c r="K119" s="2" t="s">
         <v>1727</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
+      <c r="A120" s="1">
         <v>45826</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="2" t="s">
         <v>1118</v>
       </c>
-      <c r="C120" s="3">
+      <c r="C120" s="2">
         <v>130</v>
       </c>
-      <c r="F120" s="3" t="s">
+      <c r="F120" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="J120" s="3" t="s">
+      <c r="J120" s="2" t="s">
         <v>1517</v>
       </c>
-      <c r="K120" s="3" t="s">
+      <c r="K120" s="2" t="s">
         <v>1728</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
+      <c r="A121" s="1">
         <v>45826</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="2" t="s">
         <v>1119</v>
       </c>
-      <c r="C121" s="3">
+      <c r="C121" s="2">
         <v>1381</v>
       </c>
-      <c r="F121" s="3" t="s">
+      <c r="F121" s="2" t="s">
         <v>1307</v>
       </c>
-      <c r="J121" s="3" t="s">
+      <c r="J121" s="2" t="s">
         <v>1518</v>
       </c>
-      <c r="K121" s="3" t="s">
+      <c r="K121" s="2" t="s">
         <v>1729</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
+      <c r="A122" s="1">
         <v>45831</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="C122" s="3">
+      <c r="C122" s="2">
         <v>24.2</v>
       </c>
-      <c r="F122" s="3" t="s">
+      <c r="F122" s="2" t="s">
         <v>1308</v>
       </c>
-      <c r="J122" s="3" t="s">
+      <c r="J122" s="2" t="s">
         <v>1519</v>
       </c>
-      <c r="K122" s="3" t="s">
+      <c r="K122" s="2" t="s">
         <v>1730</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
+      <c r="A123" s="1">
         <v>45832</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="C123" s="3">
+      <c r="C123" s="2">
         <v>5071.6000000000004</v>
       </c>
-      <c r="F123" s="3" t="s">
+      <c r="F123" s="2" t="s">
         <v>1309</v>
       </c>
-      <c r="J123" s="3" t="s">
+      <c r="J123" s="2" t="s">
         <v>1520</v>
       </c>
-      <c r="K123" s="3" t="s">
+      <c r="K123" s="2" t="s">
         <v>1731</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
+      <c r="A124" s="1">
         <v>45835</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="C124" s="3">
+      <c r="C124" s="2">
         <v>12.33</v>
       </c>
-      <c r="F124" s="3" t="s">
+      <c r="F124" s="2" t="s">
         <v>1310</v>
       </c>
-      <c r="J124" s="3" t="s">
+      <c r="J124" s="2" t="s">
         <v>1521</v>
       </c>
-      <c r="K124" s="3" t="s">
+      <c r="K124" s="2" t="s">
         <v>1732</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
+      <c r="A125" s="1">
         <v>45838</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="C125" s="3">
+      <c r="C125" s="2">
         <v>109.3</v>
       </c>
-      <c r="F125" s="3" t="s">
+      <c r="F125" s="2" t="s">
         <v>1311</v>
       </c>
-      <c r="J125" s="3" t="s">
+      <c r="J125" s="2" t="s">
         <v>1522</v>
       </c>
-      <c r="K125" s="3" t="s">
+      <c r="K125" s="2" t="s">
         <v>1733</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
+      <c r="A126" s="1">
         <v>45838</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="C126" s="3">
+      <c r="C126" s="2">
         <v>11068.62</v>
       </c>
-      <c r="F126" s="3" t="s">
+      <c r="F126" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="J126" s="3" t="s">
+      <c r="J126" s="2" t="s">
         <v>1523</v>
       </c>
-      <c r="K126" s="3" t="s">
+      <c r="K126" s="2" t="s">
         <v>1734</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A127" s="2">
+      <c r="A127" s="1">
         <v>45841</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="C127" s="3">
+      <c r="C127" s="2">
         <v>23</v>
       </c>
-      <c r="F127" s="3" t="s">
+      <c r="F127" s="2" t="s">
         <v>1313</v>
       </c>
-      <c r="J127" s="3" t="s">
+      <c r="J127" s="2" t="s">
         <v>1524</v>
       </c>
-      <c r="K127" s="3" t="s">
+      <c r="K127" s="2" t="s">
         <v>1735</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
+      <c r="A128" s="1">
         <v>45845</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="C128" s="3">
+      <c r="C128" s="2">
         <v>389.02</v>
       </c>
-      <c r="F128" s="3" t="s">
+      <c r="F128" s="2" t="s">
         <v>1314</v>
       </c>
-      <c r="J128" s="3" t="s">
+      <c r="J128" s="2" t="s">
         <v>1525</v>
       </c>
-      <c r="K128" s="3" t="s">
+      <c r="K128" s="2" t="s">
         <v>1736</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
+      <c r="A129" s="1">
         <v>45845</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="2" t="s">
         <v>1126</v>
       </c>
-      <c r="C129" s="3">
+      <c r="C129" s="2">
         <v>390.04</v>
       </c>
-      <c r="F129" s="3" t="s">
+      <c r="F129" s="2" t="s">
         <v>1315</v>
       </c>
-      <c r="J129" s="3" t="s">
+      <c r="J129" s="2" t="s">
         <v>1526</v>
       </c>
-      <c r="K129" s="3" t="s">
+      <c r="K129" s="2" t="s">
         <v>1737</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
+      <c r="A130" s="1">
         <v>45845</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="C130" s="3">
+      <c r="C130" s="2">
         <v>404.99</v>
       </c>
-      <c r="F130" s="3" t="s">
+      <c r="F130" s="2" t="s">
         <v>1316</v>
       </c>
-      <c r="J130" s="3" t="s">
+      <c r="J130" s="2" t="s">
         <v>1527</v>
       </c>
-      <c r="K130" s="3" t="s">
+      <c r="K130" s="2" t="s">
         <v>1738</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
+      <c r="A131" s="1">
         <v>45845</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="2" t="s">
         <v>1128</v>
       </c>
-      <c r="C131" s="3">
+      <c r="C131" s="2">
         <v>504</v>
       </c>
-      <c r="F131" s="3" t="s">
+      <c r="F131" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="J131" s="3" t="s">
+      <c r="J131" s="2" t="s">
         <v>1528</v>
       </c>
-      <c r="K131" s="3" t="s">
+      <c r="K131" s="2" t="s">
         <v>1739</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
+      <c r="A132" s="1">
         <v>45846</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="C132" s="3">
+      <c r="C132" s="2">
         <v>110.34</v>
       </c>
-      <c r="F132" s="3" t="s">
+      <c r="F132" s="2" t="s">
         <v>1318</v>
       </c>
-      <c r="J132" s="3" t="s">
+      <c r="J132" s="2" t="s">
         <v>1529</v>
       </c>
-      <c r="K132" s="3" t="s">
+      <c r="K132" s="2" t="s">
         <v>1740</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
+      <c r="A133" s="1">
         <v>45846</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="C133" s="3">
+      <c r="C133" s="2">
         <v>141.9</v>
       </c>
-      <c r="F133" s="3" t="s">
+      <c r="F133" s="2" t="s">
         <v>1319</v>
       </c>
-      <c r="J133" s="3" t="s">
+      <c r="J133" s="2" t="s">
         <v>1530</v>
       </c>
-      <c r="K133" s="3" t="s">
+      <c r="K133" s="2" t="s">
         <v>1741</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A134" s="2">
+      <c r="A134" s="1">
         <v>45846</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="C134" s="3">
+      <c r="C134" s="2">
         <v>163.01</v>
       </c>
-      <c r="F134" s="3" t="s">
+      <c r="F134" s="2" t="s">
         <v>1320</v>
       </c>
-      <c r="J134" s="3" t="s">
+      <c r="J134" s="2" t="s">
         <v>1531</v>
       </c>
-      <c r="K134" s="3" t="s">
+      <c r="K134" s="2" t="s">
         <v>1742</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
+      <c r="A135" s="1">
         <v>45846</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="C135" s="3">
+      <c r="C135" s="2">
         <v>221.01</v>
       </c>
-      <c r="F135" s="3" t="s">
+      <c r="F135" s="2" t="s">
         <v>1321</v>
       </c>
-      <c r="J135" s="3" t="s">
+      <c r="J135" s="2" t="s">
         <v>1532</v>
       </c>
-      <c r="K135" s="3" t="s">
+      <c r="K135" s="2" t="s">
         <v>1743</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A136" s="2">
+      <c r="A136" s="1">
         <v>45846</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="2" t="s">
         <v>1133</v>
       </c>
-      <c r="C136" s="3">
+      <c r="C136" s="2">
         <v>575.84</v>
       </c>
-      <c r="F136" s="3" t="s">
+      <c r="F136" s="2" t="s">
         <v>1322</v>
       </c>
-      <c r="J136" s="3" t="s">
+      <c r="J136" s="2" t="s">
         <v>1533</v>
       </c>
-      <c r="K136" s="3" t="s">
+      <c r="K136" s="2" t="s">
         <v>1744</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
+      <c r="A137" s="1">
         <v>45846</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="C137" s="3">
+      <c r="C137" s="2">
         <v>649</v>
       </c>
-      <c r="F137" s="3" t="s">
+      <c r="F137" s="2" t="s">
         <v>1323</v>
       </c>
-      <c r="J137" s="3" t="s">
+      <c r="J137" s="2" t="s">
         <v>1534</v>
       </c>
-      <c r="K137" s="3" t="s">
+      <c r="K137" s="2" t="s">
         <v>1745</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
+      <c r="A138" s="1">
         <v>45846</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="C138" s="3">
+      <c r="C138" s="2">
         <v>986.48</v>
       </c>
-      <c r="F138" s="3" t="s">
+      <c r="F138" s="2" t="s">
         <v>1324</v>
       </c>
-      <c r="J138" s="3" t="s">
+      <c r="J138" s="2" t="s">
         <v>1535</v>
       </c>
-      <c r="K138" s="3" t="s">
+      <c r="K138" s="2" t="s">
         <v>1746</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A139" s="2">
+      <c r="A139" s="1">
         <v>45848</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="C139" s="3">
+      <c r="C139" s="2">
         <v>533.20000000000005</v>
       </c>
-      <c r="F139" s="3" t="s">
+      <c r="F139" s="2" t="s">
         <v>1325</v>
       </c>
-      <c r="J139" s="3" t="s">
+      <c r="J139" s="2" t="s">
         <v>1536</v>
       </c>
-      <c r="K139" s="3" t="s">
+      <c r="K139" s="2" t="s">
         <v>1747</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
+      <c r="A140" s="1">
         <v>45852</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="C140" s="3">
+      <c r="C140" s="2">
         <v>10692.16</v>
       </c>
-      <c r="F140" s="3" t="s">
+      <c r="F140" s="2" t="s">
         <v>1326</v>
       </c>
-      <c r="J140" s="3" t="s">
+      <c r="J140" s="2" t="s">
         <v>1537</v>
       </c>
-      <c r="K140" s="3" t="s">
+      <c r="K140" s="2" t="s">
         <v>1748</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A141" s="2">
+      <c r="A141" s="1">
         <v>45855</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="C141" s="3">
+      <c r="C141" s="2">
         <v>11068.62</v>
       </c>
-      <c r="F141" s="3" t="s">
+      <c r="F141" s="2" t="s">
         <v>1327</v>
       </c>
-      <c r="J141" s="3" t="s">
+      <c r="J141" s="2" t="s">
         <v>1538</v>
       </c>
-      <c r="K141" s="3" t="s">
+      <c r="K141" s="2" t="s">
         <v>1749</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A142" s="2">
+      <c r="A142" s="1">
         <v>45856</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="C142" s="3">
+      <c r="C142" s="2">
         <v>420.8</v>
       </c>
-      <c r="F142" s="3" t="s">
+      <c r="F142" s="2" t="s">
         <v>1328</v>
       </c>
-      <c r="J142" s="3" t="s">
+      <c r="J142" s="2" t="s">
         <v>1539</v>
       </c>
-      <c r="K142" s="3" t="s">
+      <c r="K142" s="2" t="s">
         <v>1750</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A143" s="2">
+      <c r="A143" s="1">
         <v>45863</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C143" s="3">
+      <c r="C143" s="2">
         <v>82.1</v>
       </c>
-      <c r="F143" s="3" t="s">
+      <c r="F143" s="2" t="s">
         <v>1329</v>
       </c>
-      <c r="J143" s="3" t="s">
+      <c r="J143" s="2" t="s">
         <v>1540</v>
       </c>
-      <c r="K143" s="3" t="s">
+      <c r="K143" s="2" t="s">
         <v>1751</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A144" s="2">
+      <c r="A144" s="1">
         <v>45869</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="C144" s="3">
+      <c r="C144" s="2">
         <v>12897.95</v>
       </c>
-      <c r="F144" s="3" t="s">
+      <c r="F144" s="2" t="s">
         <v>1330</v>
       </c>
-      <c r="J144" s="3" t="s">
+      <c r="J144" s="2" t="s">
         <v>1541</v>
       </c>
-      <c r="K144" s="3" t="s">
+      <c r="K144" s="2" t="s">
         <v>1752</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A145" s="2">
+      <c r="A145" s="1">
         <v>45874</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="C145" s="3">
+      <c r="C145" s="2">
         <v>1299.22</v>
       </c>
-      <c r="F145" s="3" t="s">
+      <c r="F145" s="2" t="s">
         <v>1331</v>
       </c>
-      <c r="J145" s="3" t="s">
+      <c r="J145" s="2" t="s">
         <v>1542</v>
       </c>
-      <c r="K145" s="3" t="s">
+      <c r="K145" s="2" t="s">
         <v>1753</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A146" s="2">
+      <c r="A146" s="1">
         <v>45876</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" s="2" t="s">
         <v>1141</v>
       </c>
-      <c r="C146" s="3">
+      <c r="C146" s="2">
         <v>172</v>
       </c>
-      <c r="F146" s="3" t="s">
+      <c r="F146" s="2" t="s">
         <v>1332</v>
       </c>
-      <c r="J146" s="3" t="s">
+      <c r="J146" s="2" t="s">
         <v>1543</v>
       </c>
-      <c r="K146" s="3" t="s">
+      <c r="K146" s="2" t="s">
         <v>1754</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
+      <c r="A147" s="1">
         <v>45880</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C147" s="3">
+      <c r="C147" s="2">
         <v>129.69999999999999</v>
       </c>
-      <c r="F147" s="3" t="s">
+      <c r="F147" s="2" t="s">
         <v>1333</v>
       </c>
-      <c r="J147" s="3" t="s">
+      <c r="J147" s="2" t="s">
         <v>1544</v>
       </c>
-      <c r="K147" s="3" t="s">
+      <c r="K147" s="2" t="s">
         <v>1755</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A148" s="2">
+      <c r="A148" s="1">
         <v>45880</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="C148" s="3">
+      <c r="C148" s="2">
         <v>4412</v>
       </c>
-      <c r="F148" s="3" t="s">
+      <c r="F148" s="2" t="s">
         <v>1334</v>
       </c>
-      <c r="J148" s="3" t="s">
+      <c r="J148" s="2" t="s">
         <v>1545</v>
       </c>
-      <c r="K148" s="3" t="s">
+      <c r="K148" s="2" t="s">
         <v>1756</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A149" s="2">
+      <c r="A149" s="1">
         <v>45881</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" s="2" t="s">
         <v>1143</v>
       </c>
-      <c r="C149" s="3">
+      <c r="C149" s="2">
         <v>10</v>
       </c>
-      <c r="F149" s="3" t="s">
+      <c r="F149" s="2" t="s">
         <v>1335</v>
       </c>
-      <c r="J149" s="3" t="s">
+      <c r="J149" s="2" t="s">
         <v>1546</v>
       </c>
-      <c r="K149" s="3" t="s">
+      <c r="K149" s="2" t="s">
         <v>1757</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A150" s="2">
+      <c r="A150" s="1">
         <v>45881</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B150" s="2" t="s">
         <v>1143</v>
       </c>
-      <c r="C150" s="3">
+      <c r="C150" s="2">
         <v>40</v>
       </c>
-      <c r="F150" s="3" t="s">
+      <c r="F150" s="2" t="s">
         <v>1336</v>
       </c>
-      <c r="J150" s="3" t="s">
+      <c r="J150" s="2" t="s">
         <v>1547</v>
       </c>
-      <c r="K150" s="3" t="s">
+      <c r="K150" s="2" t="s">
         <v>1758</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A151" s="2">
+      <c r="A151" s="1">
         <v>45884</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="B151" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="C151" s="3">
+      <c r="C151" s="2">
         <v>165</v>
       </c>
-      <c r="F151" s="3" t="s">
+      <c r="F151" s="2" t="s">
         <v>1337</v>
       </c>
-      <c r="J151" s="3" t="s">
+      <c r="J151" s="2" t="s">
         <v>1548</v>
       </c>
-      <c r="K151" s="3" t="s">
+      <c r="K151" s="2" t="s">
         <v>1759</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A152" s="2">
+      <c r="A152" s="1">
         <v>45884</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B152" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="C152" s="3">
+      <c r="C152" s="2">
         <v>13414.24</v>
       </c>
-      <c r="F152" s="3" t="s">
+      <c r="F152" s="2" t="s">
         <v>1338</v>
       </c>
-      <c r="J152" s="3" t="s">
+      <c r="J152" s="2" t="s">
         <v>1549</v>
       </c>
-      <c r="K152" s="3" t="s">
+      <c r="K152" s="2" t="s">
         <v>1760</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A153" s="2">
+      <c r="A153" s="1">
         <v>45890</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B153" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="C153" s="3">
+      <c r="C153" s="2">
         <v>2982.91</v>
       </c>
-      <c r="F153" s="3" t="s">
+      <c r="F153" s="2" t="s">
         <v>1339</v>
       </c>
-      <c r="J153" s="3" t="s">
+      <c r="J153" s="2" t="s">
         <v>1550</v>
       </c>
-      <c r="K153" s="3" t="s">
+      <c r="K153" s="2" t="s">
         <v>1761</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A154" s="2">
+      <c r="A154" s="1">
         <v>45891</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B154" s="2" t="s">
         <v>1147</v>
       </c>
-      <c r="C154" s="3">
+      <c r="C154" s="2">
         <v>207.3</v>
       </c>
-      <c r="F154" s="3" t="s">
+      <c r="F154" s="2" t="s">
         <v>1340</v>
       </c>
-      <c r="J154" s="3" t="s">
+      <c r="J154" s="2" t="s">
         <v>1551</v>
       </c>
-      <c r="K154" s="3" t="s">
+      <c r="K154" s="2" t="s">
         <v>1762</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
+      <c r="A155" s="1">
         <v>45891</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B155" s="2" t="s">
         <v>1148</v>
       </c>
-      <c r="C155" s="3">
+      <c r="C155" s="2">
         <v>1000</v>
       </c>
-      <c r="F155" s="3" t="s">
+      <c r="F155" s="2" t="s">
         <v>1341</v>
       </c>
-      <c r="J155" s="3" t="s">
+      <c r="J155" s="2" t="s">
         <v>1552</v>
       </c>
-      <c r="K155" s="3" t="s">
+      <c r="K155" s="2" t="s">
         <v>1763</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
+      <c r="A156" s="1">
         <v>45891</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B156" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="C156" s="3">
+      <c r="C156" s="2">
         <v>2000</v>
       </c>
-      <c r="F156" s="3" t="s">
+      <c r="F156" s="2" t="s">
         <v>1342</v>
       </c>
-      <c r="J156" s="3" t="s">
+      <c r="J156" s="2" t="s">
         <v>1553</v>
       </c>
-      <c r="K156" s="3" t="s">
+      <c r="K156" s="2" t="s">
         <v>1764</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A157" s="2">
+      <c r="A157" s="1">
         <v>45895</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B157" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C157" s="3">
+      <c r="C157" s="2">
         <v>56</v>
       </c>
-      <c r="F157" s="3" t="s">
+      <c r="F157" s="2" t="s">
         <v>1343</v>
       </c>
-      <c r="J157" s="3" t="s">
+      <c r="J157" s="2" t="s">
         <v>1554</v>
       </c>
-      <c r="K157" s="3" t="s">
+      <c r="K157" s="2" t="s">
         <v>1765</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
+      <c r="A158" s="1">
         <v>45896</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B158" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C158" s="3">
+      <c r="C158" s="2">
         <v>70</v>
       </c>
-      <c r="F158" s="3" t="s">
+      <c r="F158" s="2" t="s">
         <v>1344</v>
       </c>
-      <c r="J158" s="3" t="s">
+      <c r="J158" s="2" t="s">
         <v>1555</v>
       </c>
-      <c r="K158" s="3" t="s">
+      <c r="K158" s="2" t="s">
         <v>1766</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
+      <c r="A159" s="1">
         <v>45896</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B159" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C159" s="3">
+      <c r="C159" s="2">
         <v>131.1</v>
       </c>
-      <c r="F159" s="3" t="s">
+      <c r="F159" s="2" t="s">
         <v>1345</v>
       </c>
-      <c r="J159" s="3" t="s">
+      <c r="J159" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="K159" s="3" t="s">
+      <c r="K159" s="2" t="s">
         <v>1767</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A160" s="2">
+      <c r="A160" s="1">
         <v>45898</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B160" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="C160" s="3">
+      <c r="C160" s="2">
         <v>14142.28</v>
       </c>
-      <c r="F160" s="3" t="s">
+      <c r="F160" s="2" t="s">
         <v>1346</v>
       </c>
-      <c r="J160" s="3" t="s">
+      <c r="J160" s="2" t="s">
         <v>1557</v>
       </c>
-      <c r="K160" s="3" t="s">
+      <c r="K160" s="2" t="s">
         <v>1768</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A161" s="2">
+      <c r="A161" s="1">
         <v>45910</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="C161" s="3">
+      <c r="C161" s="2">
         <v>1637.92</v>
       </c>
-      <c r="F161" s="3" t="s">
+      <c r="F161" s="2" t="s">
         <v>1347</v>
       </c>
-      <c r="J161" s="3" t="s">
+      <c r="J161" s="2" t="s">
         <v>1558</v>
       </c>
-      <c r="K161" s="3" t="s">
+      <c r="K161" s="2" t="s">
         <v>1769</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A162" s="2">
+      <c r="A162" s="1">
         <v>45912</v>
       </c>
-      <c r="B162" s="3" t="s">
+      <c r="B162" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="C162" s="3">
+      <c r="C162" s="2">
         <v>12180.4</v>
       </c>
-      <c r="F162" s="3" t="s">
+      <c r="F162" s="2" t="s">
         <v>1348</v>
       </c>
-      <c r="J162" s="3" t="s">
+      <c r="J162" s="2" t="s">
         <v>1559</v>
       </c>
-      <c r="K162" s="3" t="s">
+      <c r="K162" s="2" t="s">
         <v>1770</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A163" s="2">
+      <c r="A163" s="1">
         <v>45917</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="B163" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C163" s="3">
+      <c r="C163" s="2">
         <v>126.5</v>
       </c>
-      <c r="F163" s="3" t="s">
+      <c r="F163" s="2" t="s">
         <v>1349</v>
       </c>
-      <c r="J163" s="3" t="s">
+      <c r="J163" s="2" t="s">
         <v>1560</v>
       </c>
-      <c r="K163" s="3" t="s">
+      <c r="K163" s="2" t="s">
         <v>1771</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A164" s="2">
+      <c r="A164" s="1">
         <v>45918</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="B164" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C164" s="3">
+      <c r="C164" s="2">
         <v>190</v>
       </c>
-      <c r="F164" s="3" t="s">
+      <c r="F164" s="2" t="s">
         <v>1350</v>
       </c>
-      <c r="J164" s="3" t="s">
+      <c r="J164" s="2" t="s">
         <v>1561</v>
       </c>
-      <c r="K164" s="3" t="s">
+      <c r="K164" s="2" t="s">
         <v>1772</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A165" s="2">
+      <c r="A165" s="1">
         <v>45918</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="C165" s="3">
+      <c r="C165" s="2">
         <v>412.11</v>
       </c>
-      <c r="F165" s="3" t="s">
+      <c r="F165" s="2" t="s">
         <v>1351</v>
       </c>
-      <c r="J165" s="3" t="s">
+      <c r="J165" s="2" t="s">
         <v>1562</v>
       </c>
-      <c r="K165" s="3" t="s">
+      <c r="K165" s="2" t="s">
         <v>1773</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
+      <c r="A166" s="1">
         <v>45924</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="B166" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="C166" s="3">
+      <c r="C166" s="2">
         <v>1928.68</v>
       </c>
-      <c r="F166" s="3" t="s">
+      <c r="F166" s="2" t="s">
         <v>1352</v>
       </c>
-      <c r="J166" s="3" t="s">
+      <c r="J166" s="2" t="s">
         <v>1563</v>
       </c>
-      <c r="K166" s="3" t="s">
+      <c r="K166" s="2" t="s">
         <v>1774</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A167" s="2">
+      <c r="A167" s="1">
         <v>45929</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="B167" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="C167" s="3">
+      <c r="C167" s="2">
         <v>96.8</v>
       </c>
-      <c r="F167" s="3" t="s">
+      <c r="F167" s="2" t="s">
         <v>1353</v>
       </c>
-      <c r="J167" s="3" t="s">
+      <c r="J167" s="2" t="s">
         <v>1564</v>
       </c>
-      <c r="K167" s="3" t="s">
+      <c r="K167" s="2" t="s">
         <v>1775</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A168" s="2">
+      <c r="A168" s="1">
         <v>45929</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B168" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="C168" s="3">
+      <c r="C168" s="2">
         <v>141.61000000000001</v>
       </c>
-      <c r="F168" s="3" t="s">
+      <c r="F168" s="2" t="s">
         <v>1354</v>
       </c>
-      <c r="J168" s="3" t="s">
+      <c r="J168" s="2" t="s">
         <v>1565</v>
       </c>
-      <c r="K168" s="3" t="s">
+      <c r="K168" s="2" t="s">
         <v>1776</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A169" s="2">
+      <c r="A169" s="1">
         <v>45929</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="C169" s="3">
+      <c r="C169" s="2">
         <v>515.94000000000005</v>
       </c>
-      <c r="F169" s="3" t="s">
+      <c r="F169" s="2" t="s">
         <v>1355</v>
       </c>
-      <c r="J169" s="3" t="s">
+      <c r="J169" s="2" t="s">
         <v>1566</v>
       </c>
-      <c r="K169" s="3" t="s">
+      <c r="K169" s="2" t="s">
         <v>1777</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A170" s="2">
+      <c r="A170" s="1">
         <v>45929</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="B170" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="C170" s="3">
+      <c r="C170" s="2">
         <v>4000</v>
       </c>
-      <c r="F170" s="3" t="s">
+      <c r="F170" s="2" t="s">
         <v>1356</v>
       </c>
-      <c r="J170" s="3" t="s">
+      <c r="J170" s="2" t="s">
         <v>1567</v>
       </c>
-      <c r="K170" s="3" t="s">
+      <c r="K170" s="2" t="s">
         <v>1778</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A171" s="2">
+      <c r="A171" s="1">
         <v>45929</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="B171" s="2" t="s">
         <v>1157</v>
       </c>
-      <c r="C171" s="3">
+      <c r="C171" s="2">
         <v>11132.09</v>
       </c>
-      <c r="F171" s="3" t="s">
+      <c r="F171" s="2" t="s">
         <v>1357</v>
       </c>
-      <c r="J171" s="3" t="s">
+      <c r="J171" s="2" t="s">
         <v>1568</v>
       </c>
-      <c r="K171" s="3" t="s">
+      <c r="K171" s="2" t="s">
         <v>1779</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A172" s="2">
+      <c r="A172" s="1">
         <v>45936</v>
       </c>
-      <c r="B172" s="3" t="s">
+      <c r="B172" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="C172" s="3">
+      <c r="C172" s="2">
         <v>182.3</v>
       </c>
-      <c r="F172" s="3" t="s">
+      <c r="F172" s="2" t="s">
         <v>1358</v>
       </c>
-      <c r="J172" s="3" t="s">
+      <c r="J172" s="2" t="s">
         <v>1569</v>
       </c>
-      <c r="K172" s="3" t="s">
+      <c r="K172" s="2" t="s">
         <v>1780</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A173" s="2">
+      <c r="A173" s="1">
         <v>45936</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B173" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="C173" s="3">
+      <c r="C173" s="2">
         <v>3000</v>
       </c>
-      <c r="F173" s="3" t="s">
+      <c r="F173" s="2" t="s">
         <v>1359</v>
       </c>
-      <c r="J173" s="3" t="s">
+      <c r="J173" s="2" t="s">
         <v>1570</v>
       </c>
-      <c r="K173" s="3" t="s">
+      <c r="K173" s="2" t="s">
         <v>1781</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
+      <c r="A174" s="1">
         <v>45937</v>
       </c>
-      <c r="B174" s="3" t="s">
+      <c r="B174" s="2" t="s">
         <v>1159</v>
       </c>
-      <c r="C174" s="3">
+      <c r="C174" s="2">
         <v>372</v>
       </c>
-      <c r="F174" s="3" t="s">
+      <c r="F174" s="2" t="s">
         <v>1360</v>
       </c>
-      <c r="J174" s="3" t="s">
+      <c r="J174" s="2" t="s">
         <v>1571</v>
       </c>
-      <c r="K174" s="3" t="s">
+      <c r="K174" s="2" t="s">
         <v>1782</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A175" s="2">
+      <c r="A175" s="1">
         <v>45937</v>
       </c>
-      <c r="B175" s="3" t="s">
+      <c r="B175" s="2" t="s">
         <v>1160</v>
       </c>
-      <c r="C175" s="3">
+      <c r="C175" s="2">
         <v>1000</v>
       </c>
-      <c r="F175" s="3" t="s">
+      <c r="F175" s="2" t="s">
         <v>1361</v>
       </c>
-      <c r="J175" s="3" t="s">
+      <c r="J175" s="2" t="s">
         <v>1572</v>
       </c>
-      <c r="K175" s="3" t="s">
+      <c r="K175" s="2" t="s">
         <v>1783</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A176" s="2">
+      <c r="A176" s="1">
         <v>45939</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B176" s="2" t="s">
         <v>1161</v>
       </c>
-      <c r="C176" s="3">
+      <c r="C176" s="2">
         <v>1140</v>
       </c>
-      <c r="F176" s="3" t="s">
+      <c r="F176" s="2" t="s">
         <v>1362</v>
       </c>
-      <c r="J176" s="3" t="s">
+      <c r="J176" s="2" t="s">
         <v>1573</v>
       </c>
-      <c r="K176" s="3" t="s">
+      <c r="K176" s="2" t="s">
         <v>1784</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A177" s="2">
+      <c r="A177" s="1">
         <v>45943</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="B177" s="2" t="s">
         <v>1162</v>
       </c>
-      <c r="C177" s="3">
+      <c r="C177" s="2">
         <v>5928.68</v>
       </c>
-      <c r="F177" s="3" t="s">
+      <c r="F177" s="2" t="s">
         <v>1363</v>
       </c>
-      <c r="J177" s="3" t="s">
+      <c r="J177" s="2" t="s">
         <v>1574</v>
       </c>
-      <c r="K177" s="3" t="s">
+      <c r="K177" s="2" t="s">
         <v>1785</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A178" s="2">
+      <c r="A178" s="1">
         <v>45945</v>
       </c>
-      <c r="B178" s="3" t="s">
+      <c r="B178" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="C178" s="3">
+      <c r="C178" s="2">
         <v>12180.4</v>
       </c>
-      <c r="F178" s="3" t="s">
+      <c r="F178" s="2" t="s">
         <v>1364</v>
       </c>
-      <c r="J178" s="3" t="s">
+      <c r="J178" s="2" t="s">
         <v>1575</v>
       </c>
-      <c r="K178" s="3" t="s">
+      <c r="K178" s="2" t="s">
         <v>1786</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A179" s="2">
+      <c r="A179" s="1">
         <v>45950</v>
       </c>
-      <c r="B179" s="3" t="s">
+      <c r="B179" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C179" s="3">
+      <c r="C179" s="2">
         <v>56</v>
       </c>
-      <c r="F179" s="3" t="s">
+      <c r="F179" s="2" t="s">
         <v>1365</v>
       </c>
-      <c r="J179" s="3" t="s">
+      <c r="J179" s="2" t="s">
         <v>1576</v>
       </c>
-      <c r="K179" s="3" t="s">
+      <c r="K179" s="2" t="s">
         <v>1787</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A180" s="2">
+      <c r="A180" s="1">
         <v>45961</v>
       </c>
-      <c r="B180" s="3" t="s">
+      <c r="B180" s="2" t="s">
         <v>1164</v>
       </c>
-      <c r="C180" s="3">
+      <c r="C180" s="2">
         <v>11214.95</v>
       </c>
-      <c r="F180" s="3" t="s">
+      <c r="F180" s="2" t="s">
         <v>1366</v>
       </c>
-      <c r="J180" s="3" t="s">
+      <c r="J180" s="2" t="s">
         <v>1577</v>
       </c>
-      <c r="K180" s="3" t="s">
+      <c r="K180" s="2" t="s">
         <v>1788</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A181" s="2">
+      <c r="A181" s="1">
         <v>45964</v>
       </c>
-      <c r="B181" s="3" t="s">
+      <c r="B181" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="C181" s="3">
+      <c r="C181" s="2">
         <v>2000</v>
       </c>
-      <c r="F181" s="3" t="s">
+      <c r="F181" s="2" t="s">
         <v>1367</v>
       </c>
-      <c r="J181" s="3" t="s">
+      <c r="J181" s="2" t="s">
         <v>1578</v>
       </c>
-      <c r="K181" s="3" t="s">
+      <c r="K181" s="2" t="s">
         <v>1789</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A182" s="2">
+      <c r="A182" s="1">
         <v>45968</v>
       </c>
-      <c r="B182" s="3" t="s">
+      <c r="B182" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C182" s="3">
+      <c r="C182" s="2">
         <v>68.8</v>
       </c>
-      <c r="F182" s="3" t="s">
+      <c r="F182" s="2" t="s">
         <v>1368</v>
       </c>
-      <c r="J182" s="3" t="s">
+      <c r="J182" s="2" t="s">
         <v>1579</v>
       </c>
-      <c r="K182" s="3" t="s">
+      <c r="K182" s="2" t="s">
         <v>1790</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A183" s="2">
+      <c r="A183" s="1">
         <v>45968</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B183" s="2" t="s">
         <v>1165</v>
       </c>
-      <c r="C183" s="3">
+      <c r="C183" s="2">
         <v>2500</v>
       </c>
-      <c r="F183" s="3" t="s">
+      <c r="F183" s="2" t="s">
         <v>1369</v>
       </c>
-      <c r="J183" s="3" t="s">
+      <c r="J183" s="2" t="s">
         <v>1580</v>
       </c>
-      <c r="K183" s="3" t="s">
+      <c r="K183" s="2" t="s">
         <v>1791</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A184" s="2">
+      <c r="A184" s="1">
         <v>45973</v>
       </c>
-      <c r="B184" s="3" t="s">
+      <c r="B184" s="2" t="s">
         <v>1166</v>
       </c>
-      <c r="C184" s="3">
+      <c r="C184" s="2">
         <v>1000</v>
       </c>
-      <c r="F184" s="3" t="s">
+      <c r="F184" s="2" t="s">
         <v>1370</v>
       </c>
-      <c r="J184" s="3" t="s">
+      <c r="J184" s="2" t="s">
         <v>1581</v>
       </c>
-      <c r="K184" s="3" t="s">
+      <c r="K184" s="2" t="s">
         <v>1792</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A185" s="2">
+      <c r="A185" s="1">
         <v>45973</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="C185" s="3">
+      <c r="C185" s="2">
         <v>4000</v>
       </c>
-      <c r="F185" s="3" t="s">
+      <c r="F185" s="2" t="s">
         <v>1371</v>
       </c>
-      <c r="J185" s="3" t="s">
+      <c r="J185" s="2" t="s">
         <v>1582</v>
       </c>
-      <c r="K185" s="3" t="s">
+      <c r="K185" s="2" t="s">
         <v>1793</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A186" s="2">
+      <c r="A186" s="1">
         <v>45975</v>
       </c>
-      <c r="B186" s="3" t="s">
+      <c r="B186" s="2" t="s">
         <v>1168</v>
       </c>
-      <c r="C186" s="3">
+      <c r="C186" s="2">
         <v>11330.02</v>
       </c>
-      <c r="F186" s="3" t="s">
+      <c r="F186" s="2" t="s">
         <v>1372</v>
       </c>
-      <c r="J186" s="3" t="s">
+      <c r="J186" s="2" t="s">
         <v>1583</v>
       </c>
-      <c r="K186" s="3" t="s">
+      <c r="K186" s="2" t="s">
         <v>1794</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A187" s="2">
+      <c r="A187" s="1">
         <v>45978</v>
       </c>
-      <c r="B187" s="3" t="s">
+      <c r="B187" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C187" s="3">
+      <c r="C187" s="2">
         <v>63.5</v>
       </c>
-      <c r="F187" s="3" t="s">
+      <c r="F187" s="2" t="s">
         <v>1373</v>
       </c>
-      <c r="J187" s="3" t="s">
+      <c r="J187" s="2" t="s">
         <v>1584</v>
       </c>
-      <c r="K187" s="3" t="s">
+      <c r="K187" s="2" t="s">
         <v>1795</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A188" s="2">
+      <c r="A188" s="1">
         <v>45981</v>
       </c>
-      <c r="B188" s="3" t="s">
+      <c r="B188" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="C188" s="3">
+      <c r="C188" s="2">
         <v>1000</v>
       </c>
-      <c r="F188" s="3" t="s">
+      <c r="F188" s="2" t="s">
         <v>1374</v>
       </c>
-      <c r="J188" s="3" t="s">
+      <c r="J188" s="2" t="s">
         <v>1585</v>
       </c>
-      <c r="K188" s="3" t="s">
+      <c r="K188" s="2" t="s">
         <v>1796</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A189" s="2">
+      <c r="A189" s="1">
         <v>45985</v>
       </c>
-      <c r="B189" s="3" t="s">
+      <c r="B189" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C189" s="3">
+      <c r="C189" s="2">
         <v>80</v>
       </c>
-      <c r="F189" s="3" t="s">
+      <c r="F189" s="2" t="s">
         <v>1375</v>
       </c>
-      <c r="J189" s="3" t="s">
+      <c r="J189" s="2" t="s">
         <v>1586</v>
       </c>
-      <c r="K189" s="3" t="s">
+      <c r="K189" s="2" t="s">
         <v>1797</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A190" s="2">
+      <c r="A190" s="1">
         <v>45985</v>
       </c>
-      <c r="B190" s="3" t="s">
+      <c r="B190" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C190" s="3">
+      <c r="C190" s="2">
         <v>148.6</v>
       </c>
-      <c r="F190" s="3" t="s">
+      <c r="F190" s="2" t="s">
         <v>1376</v>
       </c>
-      <c r="J190" s="3" t="s">
+      <c r="J190" s="2" t="s">
         <v>1587</v>
       </c>
-      <c r="K190" s="3" t="s">
+      <c r="K190" s="2" t="s">
         <v>1798</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A191" s="2">
+      <c r="A191" s="1">
         <v>45987</v>
       </c>
-      <c r="B191" s="3" t="s">
+      <c r="B191" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="C191" s="3">
+      <c r="C191" s="2">
         <v>1500</v>
       </c>
-      <c r="F191" s="3" t="s">
+      <c r="F191" s="2" t="s">
         <v>1377</v>
       </c>
-      <c r="J191" s="3" t="s">
+      <c r="J191" s="2" t="s">
         <v>1588</v>
       </c>
-      <c r="K191" s="3" t="s">
+      <c r="K191" s="2" t="s">
         <v>1799</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A192" s="2">
+      <c r="A192" s="1">
         <v>45987</v>
       </c>
-      <c r="B192" s="3" t="s">
+      <c r="B192" s="2" t="s">
         <v>1170</v>
       </c>
-      <c r="C192" s="3">
+      <c r="C192" s="2">
         <v>2500</v>
       </c>
-      <c r="F192" s="3" t="s">
+      <c r="F192" s="2" t="s">
         <v>1378</v>
       </c>
-      <c r="J192" s="3" t="s">
+      <c r="J192" s="2" t="s">
         <v>1589</v>
       </c>
-      <c r="K192" s="3" t="s">
+      <c r="K192" s="2" t="s">
         <v>1800</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A193" s="2">
+      <c r="A193" s="1">
         <v>45989</v>
       </c>
-      <c r="B193" s="3" t="s">
+      <c r="B193" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="C193" s="3">
+      <c r="C193" s="2">
         <v>4717.04</v>
       </c>
-      <c r="F193" s="3" t="s">
+      <c r="F193" s="2" t="s">
         <v>1379</v>
       </c>
-      <c r="J193" s="3" t="s">
+      <c r="J193" s="2" t="s">
         <v>1590</v>
       </c>
-      <c r="K193" s="3" t="s">
+      <c r="K193" s="2" t="s">
         <v>1801</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A194" s="2">
+      <c r="A194" s="1">
         <v>45989</v>
       </c>
-      <c r="B194" s="3" t="s">
+      <c r="B194" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="C194" s="3">
+      <c r="C194" s="2">
         <v>5490.06</v>
       </c>
-      <c r="F194" s="3" t="s">
+      <c r="F194" s="2" t="s">
         <v>1380</v>
       </c>
-      <c r="J194" s="3" t="s">
+      <c r="J194" s="2" t="s">
         <v>1591</v>
       </c>
-      <c r="K194" s="3" t="s">
+      <c r="K194" s="2" t="s">
         <v>1802</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A195" s="2">
+      <c r="A195" s="1">
         <v>45989</v>
       </c>
-      <c r="B195" s="3" t="s">
+      <c r="B195" s="2" t="s">
         <v>1173</v>
       </c>
-      <c r="C195" s="3">
+      <c r="C195" s="2">
         <v>1500</v>
       </c>
-      <c r="F195" s="3" t="s">
+      <c r="F195" s="2" t="s">
         <v>1381</v>
       </c>
-      <c r="J195" s="3" t="s">
+      <c r="J195" s="2" t="s">
         <v>1592</v>
       </c>
-      <c r="K195" s="3" t="s">
+      <c r="K195" s="2" t="s">
         <v>1803</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A196" s="2">
+      <c r="A196" s="1">
         <v>45994</v>
       </c>
-      <c r="B196" s="3" t="s">
+      <c r="B196" s="2" t="s">
         <v>1174</v>
       </c>
-      <c r="C196" s="3">
+      <c r="C196" s="2">
         <v>464.12</v>
       </c>
-      <c r="F196" s="3" t="s">
+      <c r="F196" s="2" t="s">
         <v>1382</v>
       </c>
-      <c r="J196" s="3" t="s">
+      <c r="J196" s="2" t="s">
         <v>1593</v>
       </c>
-      <c r="K196" s="3" t="s">
+      <c r="K196" s="2" t="s">
         <v>1804</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A197" s="2">
+      <c r="A197" s="1">
         <v>45994</v>
       </c>
-      <c r="B197" s="3" t="s">
+      <c r="B197" s="2" t="s">
         <v>1175</v>
       </c>
-      <c r="C197" s="3">
+      <c r="C197" s="2">
         <v>1000</v>
       </c>
-      <c r="F197" s="3" t="s">
+      <c r="F197" s="2" t="s">
         <v>1383</v>
       </c>
-      <c r="J197" s="3" t="s">
+      <c r="J197" s="2" t="s">
         <v>1594</v>
       </c>
-      <c r="K197" s="3" t="s">
+      <c r="K197" s="2" t="s">
         <v>1805</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A198" s="2">
+      <c r="A198" s="1">
         <v>45994</v>
       </c>
-      <c r="B198" s="3" t="s">
+      <c r="B198" s="2" t="s">
         <v>1176</v>
       </c>
-      <c r="C198" s="3">
+      <c r="C198" s="2">
         <v>654.72</v>
       </c>
-      <c r="F198" s="3" t="s">
+      <c r="F198" s="2" t="s">
         <v>1384</v>
       </c>
-      <c r="J198" s="3" t="s">
+      <c r="J198" s="2" t="s">
         <v>1595</v>
       </c>
-      <c r="K198" s="3" t="s">
+      <c r="K198" s="2" t="s">
         <v>1806</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A199" s="2">
+      <c r="A199" s="1">
         <v>45994</v>
       </c>
-      <c r="B199" s="3" t="s">
+      <c r="B199" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="C199" s="3">
+      <c r="C199" s="2">
         <v>158.07</v>
       </c>
-      <c r="F199" s="3" t="s">
+      <c r="F199" s="2" t="s">
         <v>1385</v>
       </c>
-      <c r="J199" s="3" t="s">
+      <c r="J199" s="2" t="s">
         <v>1596</v>
       </c>
-      <c r="K199" s="3" t="s">
+      <c r="K199" s="2" t="s">
         <v>1807</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A200" s="2">
+      <c r="A200" s="1">
         <v>45994</v>
       </c>
-      <c r="B200" s="3" t="s">
+      <c r="B200" s="2" t="s">
         <v>1178</v>
       </c>
-      <c r="C200" s="3">
+      <c r="C200" s="2">
         <v>871.99</v>
       </c>
-      <c r="F200" s="3" t="s">
+      <c r="F200" s="2" t="s">
         <v>1386</v>
       </c>
-      <c r="J200" s="3" t="s">
+      <c r="J200" s="2" t="s">
         <v>1597</v>
       </c>
-      <c r="K200" s="3" t="s">
+      <c r="K200" s="2" t="s">
         <v>1808</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A201" s="2">
+      <c r="A201" s="1">
         <v>45994</v>
       </c>
-      <c r="B201" s="3" t="s">
+      <c r="B201" s="2" t="s">
         <v>1179</v>
       </c>
-      <c r="C201" s="3">
+      <c r="C201" s="2">
         <v>529.20000000000005</v>
       </c>
-      <c r="F201" s="3" t="s">
+      <c r="F201" s="2" t="s">
         <v>1387</v>
       </c>
-      <c r="J201" s="3" t="s">
+      <c r="J201" s="2" t="s">
         <v>1598</v>
       </c>
-      <c r="K201" s="3" t="s">
+      <c r="K201" s="2" t="s">
         <v>1809</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A202" s="2">
+      <c r="A202" s="1">
         <v>45995</v>
       </c>
-      <c r="B202" s="3" t="s">
+      <c r="B202" s="2" t="s">
         <v>1148</v>
       </c>
-      <c r="C202" s="3">
+      <c r="C202" s="2">
         <v>1388</v>
       </c>
-      <c r="F202" s="3" t="s">
+      <c r="F202" s="2" t="s">
         <v>1388</v>
       </c>
-      <c r="J202" s="3" t="s">
+      <c r="J202" s="2" t="s">
         <v>1599</v>
       </c>
-      <c r="K202" s="3" t="s">
+      <c r="K202" s="2" t="s">
         <v>1810</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A203" s="2">
+      <c r="A203" s="1">
         <v>46002</v>
       </c>
-      <c r="B203" s="3" t="s">
+      <c r="B203" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C203" s="3">
+      <c r="C203" s="2">
         <v>160</v>
       </c>
-      <c r="F203" s="3" t="s">
+      <c r="F203" s="2" t="s">
         <v>1389</v>
       </c>
-      <c r="J203" s="3" t="s">
+      <c r="J203" s="2" t="s">
         <v>1600</v>
       </c>
-      <c r="K203" s="3" t="s">
+      <c r="K203" s="2" t="s">
         <v>1811</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A204" s="2">
+      <c r="A204" s="1">
         <v>46003</v>
       </c>
-      <c r="B204" s="3" t="s">
+      <c r="B204" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="C204" s="3">
+      <c r="C204" s="2">
         <v>13856.1</v>
       </c>
-      <c r="F204" s="3" t="s">
+      <c r="F204" s="2" t="s">
         <v>1390</v>
       </c>
-      <c r="J204" s="3" t="s">
+      <c r="J204" s="2" t="s">
         <v>1601</v>
       </c>
-      <c r="K204" s="3" t="s">
+      <c r="K204" s="2" t="s">
         <v>1812</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A205" s="2">
+      <c r="A205" s="1">
         <v>46006</v>
       </c>
-      <c r="B205" s="3" t="s">
+      <c r="B205" s="2" t="s">
         <v>1180</v>
       </c>
-      <c r="C205" s="3">
+      <c r="C205" s="2">
         <v>11188.61</v>
       </c>
-      <c r="F205" s="3" t="s">
+      <c r="F205" s="2" t="s">
         <v>1391</v>
       </c>
-      <c r="J205" s="3" t="s">
+      <c r="J205" s="2" t="s">
         <v>1602</v>
       </c>
-      <c r="K205" s="3" t="s">
+      <c r="K205" s="2" t="s">
         <v>1813</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A206" s="2">
+      <c r="A206" s="1">
         <v>46006</v>
       </c>
-      <c r="B206" s="3" t="s">
+      <c r="B206" s="2" t="s">
         <v>1181</v>
       </c>
-      <c r="C206" s="3">
+      <c r="C206" s="2">
         <v>270</v>
       </c>
-      <c r="F206" s="3" t="s">
+      <c r="F206" s="2" t="s">
         <v>1392</v>
       </c>
-      <c r="J206" s="3" t="s">
+      <c r="J206" s="2" t="s">
         <v>1603</v>
       </c>
-      <c r="K206" s="3" t="s">
+      <c r="K206" s="2" t="s">
         <v>1814</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A207" s="2">
+      <c r="A207" s="1">
         <v>46007</v>
       </c>
-      <c r="B207" s="3" t="s">
+      <c r="B207" s="2" t="s">
         <v>1182</v>
       </c>
-      <c r="C207" s="3">
+      <c r="C207" s="2">
         <v>257.02999999999997</v>
       </c>
-      <c r="F207" s="3" t="s">
+      <c r="F207" s="2" t="s">
         <v>1393</v>
       </c>
-      <c r="J207" s="3" t="s">
+      <c r="J207" s="2" t="s">
         <v>1604</v>
       </c>
-      <c r="K207" s="3" t="s">
+      <c r="K207" s="2" t="s">
         <v>1815</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A208" s="2">
+      <c r="A208" s="1">
         <v>46008</v>
       </c>
-      <c r="B208" s="3" t="s">
+      <c r="B208" s="2" t="s">
         <v>1183</v>
       </c>
-      <c r="C208" s="3">
+      <c r="C208" s="2">
         <v>80</v>
       </c>
-      <c r="F208" s="3" t="s">
+      <c r="F208" s="2" t="s">
         <v>1394</v>
       </c>
-      <c r="J208" s="3" t="s">
+      <c r="J208" s="2" t="s">
         <v>1605</v>
       </c>
-      <c r="K208" s="3" t="s">
+      <c r="K208" s="2" t="s">
         <v>1816</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A209" s="2">
+      <c r="A209" s="1">
         <v>46008</v>
       </c>
-      <c r="B209" s="3" t="s">
+      <c r="B209" s="2" t="s">
         <v>1184</v>
       </c>
-      <c r="C209" s="3">
+      <c r="C209" s="2">
         <v>194.49</v>
       </c>
-      <c r="F209" s="3" t="s">
+      <c r="F209" s="2" t="s">
         <v>1395</v>
       </c>
-      <c r="J209" s="3" t="s">
+      <c r="J209" s="2" t="s">
         <v>1606</v>
       </c>
-      <c r="K209" s="3" t="s">
+      <c r="K209" s="2" t="s">
         <v>1817</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A210" s="2">
+      <c r="A210" s="1">
         <v>46008</v>
       </c>
-      <c r="B210" s="3" t="s">
+      <c r="B210" s="2" t="s">
         <v>1185</v>
       </c>
-      <c r="C210" s="3">
+      <c r="C210" s="2">
         <v>23.9</v>
       </c>
-      <c r="F210" s="3" t="s">
+      <c r="F210" s="2" t="s">
         <v>1396</v>
       </c>
-      <c r="J210" s="3" t="s">
+      <c r="J210" s="2" t="s">
         <v>1607</v>
       </c>
-      <c r="K210" s="3" t="s">
+      <c r="K210" s="2" t="s">
         <v>1818</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A211" s="2">
+      <c r="A211" s="1">
         <v>46020</v>
       </c>
-      <c r="B211" s="3" t="s">
+      <c r="B211" s="2" t="s">
         <v>1186</v>
       </c>
-      <c r="C211" s="3">
+      <c r="C211" s="2">
         <v>13106.07</v>
       </c>
-      <c r="F211" s="3" t="s">
+      <c r="F211" s="2" t="s">
         <v>1397</v>
       </c>
-      <c r="J211" s="3" t="s">
+      <c r="J211" s="2" t="s">
         <v>1608</v>
       </c>
-      <c r="K211" s="3" t="s">
+      <c r="K211" s="2" t="s">
         <v>1819</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A212" s="2">
+      <c r="A212" s="1">
         <v>46020</v>
       </c>
-      <c r="B212" s="3" t="s">
+      <c r="B212" s="2" t="s">
         <v>1187</v>
       </c>
-      <c r="C212" s="3">
+      <c r="C212" s="2">
         <v>2000</v>
       </c>
-      <c r="F212" s="3" t="s">
+      <c r="F212" s="2" t="s">
         <v>1398</v>
       </c>
-      <c r="J212" s="3" t="s">
+      <c r="J212" s="2" t="s">
         <v>1609</v>
       </c>
-      <c r="K212" s="3" t="s">
+      <c r="K212" s="2" t="s">
         <v>1820</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A213" s="2">
+      <c r="A213" s="1">
         <v>45729</v>
       </c>
       <c r="B213" t="s">
@@ -10170,7 +10176,7 @@
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A214" s="2">
+      <c r="A214" s="1">
         <v>45730</v>
       </c>
       <c r="B214" t="s">
@@ -10190,7 +10196,7 @@
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A215" s="2">
+      <c r="A215" s="1">
         <v>45730</v>
       </c>
       <c r="B215" t="s">
@@ -10210,7 +10216,7 @@
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A216" s="2">
+      <c r="A216" s="1">
         <v>45730</v>
       </c>
       <c r="B216" t="s">
@@ -10230,7 +10236,7 @@
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A217" s="2">
+      <c r="A217" s="1">
         <v>45730</v>
       </c>
       <c r="B217" t="s">
@@ -10250,7 +10256,7 @@
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A218" s="2">
+      <c r="A218" s="1">
         <v>45730</v>
       </c>
       <c r="B218" t="s">
@@ -10270,7 +10276,7 @@
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A219" s="2">
+      <c r="A219" s="1">
         <v>45733</v>
       </c>
       <c r="B219" t="s">
@@ -10290,7 +10296,7 @@
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A220" s="2">
+      <c r="A220" s="1">
         <v>45733</v>
       </c>
       <c r="B220" t="s">
@@ -10310,7 +10316,7 @@
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A221" s="2">
+      <c r="A221" s="1">
         <v>45733</v>
       </c>
       <c r="B221" t="s">
@@ -10330,7 +10336,7 @@
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A222" s="2">
+      <c r="A222" s="1">
         <v>45734</v>
       </c>
       <c r="B222" t="s">
@@ -10350,7 +10356,7 @@
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A223" s="2">
+      <c r="A223" s="1">
         <v>45734</v>
       </c>
       <c r="B223" t="s">
@@ -10370,7 +10376,7 @@
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A224" s="2">
+      <c r="A224" s="1">
         <v>45735</v>
       </c>
       <c r="B224" t="s">
@@ -10390,7 +10396,7 @@
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A225" s="2">
+      <c r="A225" s="1">
         <v>45735</v>
       </c>
       <c r="B225" t="s">
@@ -10410,7 +10416,7 @@
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A226" s="2">
+      <c r="A226" s="1">
         <v>45736</v>
       </c>
       <c r="B226" t="s">
@@ -10430,7 +10436,7 @@
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A227" s="2">
+      <c r="A227" s="1">
         <v>45736</v>
       </c>
       <c r="B227" t="s">
@@ -10450,7 +10456,7 @@
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A228" s="2">
+      <c r="A228" s="1">
         <v>45736</v>
       </c>
       <c r="B228" t="s">
@@ -10470,7 +10476,7 @@
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A229" s="2">
+      <c r="A229" s="1">
         <v>45736</v>
       </c>
       <c r="B229" t="s">
@@ -10490,7 +10496,7 @@
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A230" s="2">
+      <c r="A230" s="1">
         <v>45736</v>
       </c>
       <c r="B230" t="s">
@@ -10510,7 +10516,7 @@
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A231" s="2">
+      <c r="A231" s="1">
         <v>45736</v>
       </c>
       <c r="B231" t="s">
@@ -10530,7 +10536,7 @@
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A232" s="2">
+      <c r="A232" s="1">
         <v>45737</v>
       </c>
       <c r="B232" t="s">
@@ -10550,7 +10556,7 @@
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A233" s="2">
+      <c r="A233" s="1">
         <v>45737</v>
       </c>
       <c r="B233" t="s">
@@ -10570,7 +10576,7 @@
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A234" s="2">
+      <c r="A234" s="1">
         <v>45737</v>
       </c>
       <c r="B234" t="s">
@@ -10590,7 +10596,7 @@
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A235" s="2">
+      <c r="A235" s="1">
         <v>45740</v>
       </c>
       <c r="B235" t="s">
@@ -10610,7 +10616,7 @@
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A236" s="2">
+      <c r="A236" s="1">
         <v>45740</v>
       </c>
       <c r="B236" t="s">
@@ -10630,7 +10636,7 @@
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A237" s="2">
+      <c r="A237" s="1">
         <v>45740</v>
       </c>
       <c r="B237" t="s">
@@ -10650,7 +10656,7 @@
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A238" s="2">
+      <c r="A238" s="1">
         <v>45741</v>
       </c>
       <c r="B238" t="s">
@@ -10670,7 +10676,7 @@
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A239" s="2">
+      <c r="A239" s="1">
         <v>45741</v>
       </c>
       <c r="B239" t="s">
@@ -10690,7 +10696,7 @@
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A240" s="2">
+      <c r="A240" s="1">
         <v>45741</v>
       </c>
       <c r="B240" t="s">
@@ -10710,7 +10716,7 @@
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A241" s="2">
+      <c r="A241" s="1">
         <v>45741</v>
       </c>
       <c r="B241" t="s">
@@ -10730,7 +10736,7 @@
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A242" s="2">
+      <c r="A242" s="1">
         <v>45741</v>
       </c>
       <c r="B242" t="s">
@@ -10750,7 +10756,7 @@
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A243" s="2">
+      <c r="A243" s="1">
         <v>45741</v>
       </c>
       <c r="B243" t="s">
@@ -10770,7 +10776,7 @@
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A244" s="2">
+      <c r="A244" s="1">
         <v>45742</v>
       </c>
       <c r="B244" t="s">
@@ -10790,7 +10796,7 @@
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A245" s="2">
+      <c r="A245" s="1">
         <v>45742</v>
       </c>
       <c r="B245" t="s">
@@ -10810,7 +10816,7 @@
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A246" s="2">
+      <c r="A246" s="1">
         <v>45742</v>
       </c>
       <c r="B246" t="s">
@@ -10830,7 +10836,7 @@
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A247" s="2">
+      <c r="A247" s="1">
         <v>45742</v>
       </c>
       <c r="B247" t="s">
@@ -10850,7 +10856,7 @@
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A248" s="2">
+      <c r="A248" s="1">
         <v>45742</v>
       </c>
       <c r="B248" t="s">
@@ -10870,7 +10876,7 @@
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A249" s="2">
+      <c r="A249" s="1">
         <v>45742</v>
       </c>
       <c r="B249" t="s">
@@ -10890,7 +10896,7 @@
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A250" s="2">
+      <c r="A250" s="1">
         <v>45742</v>
       </c>
       <c r="B250" t="s">
@@ -10910,7 +10916,7 @@
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A251" s="2">
+      <c r="A251" s="1">
         <v>45743</v>
       </c>
       <c r="B251" t="s">
@@ -10930,7 +10936,7 @@
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A252" s="2">
+      <c r="A252" s="1">
         <v>45744</v>
       </c>
       <c r="B252" t="s">
@@ -10950,7 +10956,7 @@
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A253" s="2">
+      <c r="A253" s="1">
         <v>45744</v>
       </c>
       <c r="B253" t="s">
@@ -10970,7 +10976,7 @@
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A254" s="2">
+      <c r="A254" s="1">
         <v>45747</v>
       </c>
       <c r="B254" t="s">
@@ -10990,7 +10996,7 @@
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A255" s="2">
+      <c r="A255" s="1">
         <v>45747</v>
       </c>
       <c r="B255" t="s">
@@ -11010,7 +11016,7 @@
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A256" s="2">
+      <c r="A256" s="1">
         <v>45747</v>
       </c>
       <c r="B256" t="s">
@@ -11030,7 +11036,7 @@
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A257" s="2">
+      <c r="A257" s="1">
         <v>45747</v>
       </c>
       <c r="B257" t="s">
@@ -11050,7 +11056,7 @@
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A258" s="2">
+      <c r="A258" s="1">
         <v>45748</v>
       </c>
       <c r="B258" t="s">
@@ -11070,7 +11076,7 @@
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A259" s="2">
+      <c r="A259" s="1">
         <v>45749</v>
       </c>
       <c r="B259" t="s">
@@ -11090,7 +11096,7 @@
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A260" s="2">
+      <c r="A260" s="1">
         <v>45749</v>
       </c>
       <c r="B260" t="s">
@@ -11110,7 +11116,7 @@
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A261" s="2">
+      <c r="A261" s="1">
         <v>45749</v>
       </c>
       <c r="B261" t="s">
@@ -11130,7 +11136,7 @@
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A262" s="2">
+      <c r="A262" s="1">
         <v>45749</v>
       </c>
       <c r="B262" t="s">
@@ -11150,7 +11156,7 @@
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A263" s="2">
+      <c r="A263" s="1">
         <v>45750</v>
       </c>
       <c r="B263" t="s">
@@ -11170,7 +11176,7 @@
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A264" s="2">
+      <c r="A264" s="1">
         <v>45750</v>
       </c>
       <c r="B264" t="s">
@@ -11190,7 +11196,7 @@
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A265" s="2">
+      <c r="A265" s="1">
         <v>45750</v>
       </c>
       <c r="B265" t="s">
@@ -11210,7 +11216,7 @@
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A266" s="2">
+      <c r="A266" s="1">
         <v>45750</v>
       </c>
       <c r="B266" t="s">
@@ -11230,7 +11236,7 @@
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A267" s="2">
+      <c r="A267" s="1">
         <v>45754</v>
       </c>
       <c r="B267" t="s">
@@ -11250,7 +11256,7 @@
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A268" s="2">
+      <c r="A268" s="1">
         <v>45755</v>
       </c>
       <c r="B268" t="s">
@@ -11270,7 +11276,7 @@
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A269" s="2">
+      <c r="A269" s="1">
         <v>45755</v>
       </c>
       <c r="B269" t="s">
@@ -11290,7 +11296,7 @@
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A270" s="2">
+      <c r="A270" s="1">
         <v>45755</v>
       </c>
       <c r="B270" t="s">
@@ -11310,7 +11316,7 @@
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A271" s="2">
+      <c r="A271" s="1">
         <v>45755</v>
       </c>
       <c r="B271" t="s">
@@ -11330,7 +11336,7 @@
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A272" s="2">
+      <c r="A272" s="1">
         <v>45755</v>
       </c>
       <c r="B272" t="s">
@@ -11350,7 +11356,7 @@
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A273" s="2">
+      <c r="A273" s="1">
         <v>45756</v>
       </c>
       <c r="B273" t="s">
@@ -11370,7 +11376,7 @@
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A274" s="2">
+      <c r="A274" s="1">
         <v>45756</v>
       </c>
       <c r="B274" t="s">
@@ -11390,7 +11396,7 @@
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A275" s="2">
+      <c r="A275" s="1">
         <v>45756</v>
       </c>
       <c r="B275" t="s">
@@ -11410,7 +11416,7 @@
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A276" s="2">
+      <c r="A276" s="1">
         <v>45756</v>
       </c>
       <c r="B276" t="s">
@@ -11430,7 +11436,7 @@
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A277" s="2">
+      <c r="A277" s="1">
         <v>45756</v>
       </c>
       <c r="B277" t="s">
@@ -11450,7 +11456,7 @@
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A278" s="2">
+      <c r="A278" s="1">
         <v>45758</v>
       </c>
       <c r="B278" t="s">
@@ -11470,7 +11476,7 @@
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A279" s="2">
+      <c r="A279" s="1">
         <v>45758</v>
       </c>
       <c r="B279" t="s">
@@ -11490,7 +11496,7 @@
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A280" s="2">
+      <c r="A280" s="1">
         <v>45761</v>
       </c>
       <c r="B280" t="s">
@@ -11510,7 +11516,7 @@
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A281" s="2">
+      <c r="A281" s="1">
         <v>45761</v>
       </c>
       <c r="B281" t="s">
@@ -11530,7 +11536,7 @@
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A282" s="2">
+      <c r="A282" s="1">
         <v>45761</v>
       </c>
       <c r="B282" t="s">
@@ -11550,7 +11556,7 @@
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A283" s="2">
+      <c r="A283" s="1">
         <v>45762</v>
       </c>
       <c r="B283" t="s">
@@ -11570,7 +11576,7 @@
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A284" s="2">
+      <c r="A284" s="1">
         <v>45762</v>
       </c>
       <c r="B284" t="s">
@@ -11590,7 +11596,7 @@
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A285" s="2">
+      <c r="A285" s="1">
         <v>45762</v>
       </c>
       <c r="B285" t="s">
@@ -11610,7 +11616,7 @@
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A286" s="2">
+      <c r="A286" s="1">
         <v>45762</v>
       </c>
       <c r="B286" t="s">
@@ -11630,7 +11636,7 @@
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A287" s="2">
+      <c r="A287" s="1">
         <v>45763</v>
       </c>
       <c r="B287" t="s">
@@ -11650,7 +11656,7 @@
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A288" s="2">
+      <c r="A288" s="1">
         <v>45763</v>
       </c>
       <c r="B288" t="s">
@@ -11670,7 +11676,7 @@
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A289" s="2">
+      <c r="A289" s="1">
         <v>45763</v>
       </c>
       <c r="B289" t="s">
@@ -11690,7 +11696,7 @@
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A290" s="2">
+      <c r="A290" s="1">
         <v>45763</v>
       </c>
       <c r="B290" t="s">
@@ -11710,7 +11716,7 @@
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A291" s="2">
+      <c r="A291" s="1">
         <v>45768</v>
       </c>
       <c r="B291" t="s">
@@ -11730,7 +11736,7 @@
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A292" s="2">
+      <c r="A292" s="1">
         <v>45768</v>
       </c>
       <c r="B292" t="s">
@@ -11750,7 +11756,7 @@
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A293" s="2">
+      <c r="A293" s="1">
         <v>45768</v>
       </c>
       <c r="B293" t="s">
@@ -11770,7 +11776,7 @@
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A294" s="2">
+      <c r="A294" s="1">
         <v>45769</v>
       </c>
       <c r="B294" t="s">
@@ -11790,7 +11796,7 @@
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A295" s="2">
+      <c r="A295" s="1">
         <v>45769</v>
       </c>
       <c r="B295" t="s">
@@ -11810,7 +11816,7 @@
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A296" s="2">
+      <c r="A296" s="1">
         <v>45769</v>
       </c>
       <c r="B296" t="s">
@@ -11830,7 +11836,7 @@
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A297" s="2">
+      <c r="A297" s="1">
         <v>45769</v>
       </c>
       <c r="B297" t="s">
@@ -11850,7 +11856,7 @@
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A298" s="2">
+      <c r="A298" s="1">
         <v>45770</v>
       </c>
       <c r="B298" t="s">
@@ -11870,7 +11876,7 @@
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A299" s="2">
+      <c r="A299" s="1">
         <v>45771</v>
       </c>
       <c r="B299" t="s">
@@ -11890,7 +11896,7 @@
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A300" s="2">
+      <c r="A300" s="1">
         <v>45771</v>
       </c>
       <c r="B300" t="s">
@@ -11910,7 +11916,7 @@
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A301" s="2">
+      <c r="A301" s="1">
         <v>45771</v>
       </c>
       <c r="B301" t="s">
@@ -11930,7 +11936,7 @@
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A302" s="2">
+      <c r="A302" s="1">
         <v>45772</v>
       </c>
       <c r="B302" t="s">
@@ -11950,7 +11956,7 @@
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A303" s="2">
+      <c r="A303" s="1">
         <v>45775</v>
       </c>
       <c r="B303" t="s">
@@ -11970,7 +11976,7 @@
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A304" s="2">
+      <c r="A304" s="1">
         <v>45775</v>
       </c>
       <c r="B304" t="s">
@@ -11990,7 +11996,7 @@
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A305" s="2">
+      <c r="A305" s="1">
         <v>45776</v>
       </c>
       <c r="B305" t="s">
@@ -12010,7 +12016,7 @@
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A306" s="2">
+      <c r="A306" s="1">
         <v>45776</v>
       </c>
       <c r="B306" t="s">
@@ -12030,7 +12036,7 @@
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A307" s="2">
+      <c r="A307" s="1">
         <v>45776</v>
       </c>
       <c r="B307" t="s">
@@ -12050,7 +12056,7 @@
       </c>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A308" s="2">
+      <c r="A308" s="1">
         <v>45776</v>
       </c>
       <c r="B308" t="s">
@@ -12070,7 +12076,7 @@
       </c>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A309" s="2">
+      <c r="A309" s="1">
         <v>45777</v>
       </c>
       <c r="B309" t="s">
@@ -12090,7 +12096,7 @@
       </c>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A310" s="2">
+      <c r="A310" s="1">
         <v>45777</v>
       </c>
       <c r="B310" t="s">
@@ -12110,7 +12116,7 @@
       </c>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A311" s="2">
+      <c r="A311" s="1">
         <v>45779</v>
       </c>
       <c r="B311" t="s">
@@ -12130,7 +12136,7 @@
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A312" s="2">
+      <c r="A312" s="1">
         <v>45779</v>
       </c>
       <c r="B312" t="s">
@@ -12150,7 +12156,7 @@
       </c>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A313" s="2">
+      <c r="A313" s="1">
         <v>45779</v>
       </c>
       <c r="B313" t="s">
@@ -12170,7 +12176,7 @@
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A314" s="2">
+      <c r="A314" s="1">
         <v>45779</v>
       </c>
       <c r="B314" t="s">
@@ -12190,7 +12196,7 @@
       </c>
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A315" s="2">
+      <c r="A315" s="1">
         <v>45783</v>
       </c>
       <c r="B315" t="s">
@@ -12210,7 +12216,7 @@
       </c>
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A316" s="2">
+      <c r="A316" s="1">
         <v>45784</v>
       </c>
       <c r="B316" t="s">
@@ -12230,7 +12236,7 @@
       </c>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A317" s="2">
+      <c r="A317" s="1">
         <v>45784</v>
       </c>
       <c r="B317" t="s">
@@ -12250,7 +12256,7 @@
       </c>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A318" s="2">
+      <c r="A318" s="1">
         <v>45784</v>
       </c>
       <c r="B318" t="s">
@@ -12270,7 +12276,7 @@
       </c>
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A319" s="2">
+      <c r="A319" s="1">
         <v>45784</v>
       </c>
       <c r="B319" t="s">
@@ -12290,7 +12296,7 @@
       </c>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A320" s="2">
+      <c r="A320" s="1">
         <v>45784</v>
       </c>
       <c r="B320" t="s">
@@ -12310,7 +12316,7 @@
       </c>
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A321" s="2">
+      <c r="A321" s="1">
         <v>45785</v>
       </c>
       <c r="B321" t="s">
@@ -12330,7 +12336,7 @@
       </c>
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A322" s="2">
+      <c r="A322" s="1">
         <v>45785</v>
       </c>
       <c r="B322" t="s">
@@ -12350,7 +12356,7 @@
       </c>
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A323" s="2">
+      <c r="A323" s="1">
         <v>45785</v>
       </c>
       <c r="B323" t="s">
@@ -12370,7 +12376,7 @@
       </c>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A324" s="2">
+      <c r="A324" s="1">
         <v>45785</v>
       </c>
       <c r="B324" t="s">
@@ -12390,7 +12396,7 @@
       </c>
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A325" s="2">
+      <c r="A325" s="1">
         <v>45785</v>
       </c>
       <c r="B325" t="s">
@@ -12410,7 +12416,7 @@
       </c>
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A326" s="2">
+      <c r="A326" s="1">
         <v>45785</v>
       </c>
       <c r="B326" t="s">
@@ -12430,7 +12436,7 @@
       </c>
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A327" s="2">
+      <c r="A327" s="1">
         <v>45786</v>
       </c>
       <c r="B327" t="s">
@@ -12450,7 +12456,7 @@
       </c>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A328" s="2">
+      <c r="A328" s="1">
         <v>45786</v>
       </c>
       <c r="B328" t="s">
@@ -12470,7 +12476,7 @@
       </c>
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A329" s="2">
+      <c r="A329" s="1">
         <v>45786</v>
       </c>
       <c r="B329" t="s">
@@ -12490,7 +12496,7 @@
       </c>
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A330" s="2">
+      <c r="A330" s="1">
         <v>45786</v>
       </c>
       <c r="B330" t="s">
@@ -12510,7 +12516,7 @@
       </c>
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A331" s="2">
+      <c r="A331" s="1">
         <v>45786</v>
       </c>
       <c r="B331" t="s">
@@ -12530,7 +12536,7 @@
       </c>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A332" s="2">
+      <c r="A332" s="1">
         <v>45786</v>
       </c>
       <c r="B332" t="s">
@@ -12550,7 +12556,7 @@
       </c>
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A333" s="2">
+      <c r="A333" s="1">
         <v>45789</v>
       </c>
       <c r="B333" t="s">
@@ -12570,7 +12576,7 @@
       </c>
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A334" s="2">
+      <c r="A334" s="1">
         <v>45789</v>
       </c>
       <c r="B334" t="s">
@@ -12590,7 +12596,7 @@
       </c>
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A335" s="2">
+      <c r="A335" s="1">
         <v>45789</v>
       </c>
       <c r="B335" t="s">
@@ -12610,7 +12616,7 @@
       </c>
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A336" s="2">
+      <c r="A336" s="1">
         <v>45789</v>
       </c>
       <c r="B336" t="s">
@@ -12630,7 +12636,7 @@
       </c>
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A337" s="2">
+      <c r="A337" s="1">
         <v>45789</v>
       </c>
       <c r="B337" t="s">
@@ -12650,7 +12656,7 @@
       </c>
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A338" s="2">
+      <c r="A338" s="1">
         <v>45791</v>
       </c>
       <c r="B338" t="s">
@@ -12670,7 +12676,7 @@
       </c>
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A339" s="2">
+      <c r="A339" s="1">
         <v>45792</v>
       </c>
       <c r="B339" t="s">
@@ -12690,7 +12696,7 @@
       </c>
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A340" s="2">
+      <c r="A340" s="1">
         <v>45792</v>
       </c>
       <c r="B340" t="s">
@@ -12710,7 +12716,7 @@
       </c>
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A341" s="2">
+      <c r="A341" s="1">
         <v>45792</v>
       </c>
       <c r="B341" t="s">
@@ -12730,7 +12736,7 @@
       </c>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A342" s="2">
+      <c r="A342" s="1">
         <v>45792</v>
       </c>
       <c r="B342" t="s">
@@ -12750,7 +12756,7 @@
       </c>
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A343" s="2">
+      <c r="A343" s="1">
         <v>45792</v>
       </c>
       <c r="B343" t="s">
@@ -12770,7 +12776,7 @@
       </c>
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A344" s="2">
+      <c r="A344" s="1">
         <v>45792</v>
       </c>
       <c r="B344" t="s">
@@ -12790,7 +12796,7 @@
       </c>
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A345" s="2">
+      <c r="A345" s="1">
         <v>45793</v>
       </c>
       <c r="B345" t="s">
@@ -12810,7 +12816,7 @@
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A346" s="2">
+      <c r="A346" s="1">
         <v>45795</v>
       </c>
       <c r="B346" t="s">
@@ -12830,7 +12836,7 @@
       </c>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A347" s="2">
+      <c r="A347" s="1">
         <v>45796</v>
       </c>
       <c r="B347" t="s">
@@ -12850,7 +12856,7 @@
       </c>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A348" s="2">
+      <c r="A348" s="1">
         <v>45796</v>
       </c>
       <c r="B348" t="s">
@@ -12870,7 +12876,7 @@
       </c>
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A349" s="2">
+      <c r="A349" s="1">
         <v>45797</v>
       </c>
       <c r="B349" t="s">
@@ -12890,7 +12896,7 @@
       </c>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A350" s="2">
+      <c r="A350" s="1">
         <v>45797</v>
       </c>
       <c r="B350" t="s">
@@ -12910,7 +12916,7 @@
       </c>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A351" s="2">
+      <c r="A351" s="1">
         <v>45798</v>
       </c>
       <c r="B351" t="s">
@@ -12930,7 +12936,7 @@
       </c>
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A352" s="2">
+      <c r="A352" s="1">
         <v>45798</v>
       </c>
       <c r="B352" t="s">
@@ -12950,7 +12956,7 @@
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A353" s="2">
+      <c r="A353" s="1">
         <v>45798</v>
       </c>
       <c r="B353" t="s">
@@ -12970,7 +12976,7 @@
       </c>
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A354" s="2">
+      <c r="A354" s="1">
         <v>45799</v>
       </c>
       <c r="B354" t="s">
@@ -12990,7 +12996,7 @@
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A355" s="2">
+      <c r="A355" s="1">
         <v>45799</v>
       </c>
       <c r="B355" t="s">
@@ -13010,7 +13016,7 @@
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A356" s="2">
+      <c r="A356" s="1">
         <v>45799</v>
       </c>
       <c r="B356" t="s">
@@ -13030,7 +13036,7 @@
       </c>
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A357" s="2">
+      <c r="A357" s="1">
         <v>45799</v>
       </c>
       <c r="B357" t="s">
@@ -13050,7 +13056,7 @@
       </c>
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A358" s="2">
+      <c r="A358" s="1">
         <v>45799</v>
       </c>
       <c r="B358" t="s">
@@ -13070,7 +13076,7 @@
       </c>
     </row>
     <row r="359" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A359" s="2">
+      <c r="A359" s="1">
         <v>45799</v>
       </c>
       <c r="B359" t="s">
@@ -13090,7 +13096,7 @@
       </c>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A360" s="2">
+      <c r="A360" s="1">
         <v>45799</v>
       </c>
       <c r="B360" t="s">
@@ -13110,7 +13116,7 @@
       </c>
     </row>
     <row r="361" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A361" s="2">
+      <c r="A361" s="1">
         <v>45803</v>
       </c>
       <c r="B361" t="s">
@@ -13130,7 +13136,7 @@
       </c>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A362" s="2">
+      <c r="A362" s="1">
         <v>45803</v>
       </c>
       <c r="B362" t="s">
@@ -13150,7 +13156,7 @@
       </c>
     </row>
     <row r="363" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A363" s="2">
+      <c r="A363" s="1">
         <v>45803</v>
       </c>
       <c r="B363" t="s">
@@ -13170,7 +13176,7 @@
       </c>
     </row>
     <row r="364" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A364" s="2">
+      <c r="A364" s="1">
         <v>45804</v>
       </c>
       <c r="B364" t="s">
@@ -13190,7 +13196,7 @@
       </c>
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A365" s="2">
+      <c r="A365" s="1">
         <v>45804</v>
       </c>
       <c r="B365" t="s">
@@ -13210,7 +13216,7 @@
       </c>
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A366" s="2">
+      <c r="A366" s="1">
         <v>45804</v>
       </c>
       <c r="B366" t="s">
@@ -13230,7 +13236,7 @@
       </c>
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A367" s="2">
+      <c r="A367" s="1">
         <v>45804</v>
       </c>
       <c r="B367" t="s">
@@ -13250,7 +13256,7 @@
       </c>
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A368" s="2">
+      <c r="A368" s="1">
         <v>45805</v>
       </c>
       <c r="B368" t="s">
@@ -13270,7 +13276,7 @@
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A369" s="2">
+      <c r="A369" s="1">
         <v>45805</v>
       </c>
       <c r="B369" t="s">
@@ -13290,7 +13296,7 @@
       </c>
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A370" s="2">
+      <c r="A370" s="1">
         <v>45805</v>
       </c>
       <c r="B370" t="s">
@@ -13310,7 +13316,7 @@
       </c>
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A371" s="2">
+      <c r="A371" s="1">
         <v>45805</v>
       </c>
       <c r="B371" t="s">
@@ -13330,7 +13336,7 @@
       </c>
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A372" s="2">
+      <c r="A372" s="1">
         <v>45805</v>
       </c>
       <c r="B372" t="s">
@@ -13350,7 +13356,7 @@
       </c>
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A373" s="2">
+      <c r="A373" s="1">
         <v>45807</v>
       </c>
       <c r="B373" t="s">
@@ -13370,7 +13376,7 @@
       </c>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A374" s="2">
+      <c r="A374" s="1">
         <v>45807</v>
       </c>
       <c r="B374" t="s">
@@ -13390,7 +13396,7 @@
       </c>
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A375" s="2">
+      <c r="A375" s="1">
         <v>45807</v>
       </c>
       <c r="B375" t="s">
@@ -13410,7 +13416,7 @@
       </c>
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A376" s="2">
+      <c r="A376" s="1">
         <v>45807</v>
       </c>
       <c r="B376" t="s">
@@ -13430,7 +13436,7 @@
       </c>
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A377" s="2">
+      <c r="A377" s="1">
         <v>45807</v>
       </c>
       <c r="B377" t="s">
@@ -13450,7 +13456,7 @@
       </c>
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A378" s="2">
+      <c r="A378" s="1">
         <v>45808</v>
       </c>
       <c r="B378" t="s">
@@ -13470,7 +13476,7 @@
       </c>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A379" s="2">
+      <c r="A379" s="1">
         <v>45808</v>
       </c>
       <c r="B379" t="s">
@@ -13490,7 +13496,7 @@
       </c>
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A380" s="2">
+      <c r="A380" s="1">
         <v>45810</v>
       </c>
       <c r="B380" t="s">
@@ -13510,7 +13516,7 @@
       </c>
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A381" s="2">
+      <c r="A381" s="1">
         <v>45810</v>
       </c>
       <c r="B381" t="s">
@@ -13530,7 +13536,7 @@
       </c>
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A382" s="2">
+      <c r="A382" s="1">
         <v>45810</v>
       </c>
       <c r="B382" t="s">
@@ -13550,7 +13556,7 @@
       </c>
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A383" s="2">
+      <c r="A383" s="1">
         <v>45810</v>
       </c>
       <c r="B383" t="s">
@@ -13570,7 +13576,7 @@
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A384" s="2">
+      <c r="A384" s="1">
         <v>45810</v>
       </c>
       <c r="B384" t="s">
@@ -13590,7 +13596,7 @@
       </c>
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A385" s="2">
+      <c r="A385" s="1">
         <v>45810</v>
       </c>
       <c r="B385" t="s">
@@ -13610,7 +13616,7 @@
       </c>
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A386" s="2">
+      <c r="A386" s="1">
         <v>45810</v>
       </c>
       <c r="B386" t="s">
@@ -13630,7 +13636,7 @@
       </c>
     </row>
     <row r="387" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A387" s="2">
+      <c r="A387" s="1">
         <v>45811</v>
       </c>
       <c r="B387" t="s">
@@ -13650,7 +13656,7 @@
       </c>
     </row>
     <row r="388" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A388" s="2">
+      <c r="A388" s="1">
         <v>45811</v>
       </c>
       <c r="B388" t="s">
@@ -13670,7 +13676,7 @@
       </c>
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A389" s="2">
+      <c r="A389" s="1">
         <v>45812</v>
       </c>
       <c r="B389" t="s">
@@ -13690,7 +13696,7 @@
       </c>
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A390" s="2">
+      <c r="A390" s="1">
         <v>45814</v>
       </c>
       <c r="B390" t="s">
@@ -13710,7 +13716,7 @@
       </c>
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A391" s="2">
+      <c r="A391" s="1">
         <v>45814</v>
       </c>
       <c r="B391" t="s">
@@ -13730,7 +13736,7 @@
       </c>
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A392" s="2">
+      <c r="A392" s="1">
         <v>45820</v>
       </c>
       <c r="B392" t="s">
@@ -13750,7 +13756,7 @@
       </c>
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A393" s="2">
+      <c r="A393" s="1">
         <v>45820</v>
       </c>
       <c r="B393" t="s">
@@ -13770,7 +13776,7 @@
       </c>
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A394" s="2">
+      <c r="A394" s="1">
         <v>45820</v>
       </c>
       <c r="B394" t="s">
@@ -13790,7 +13796,7 @@
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A395" s="2">
+      <c r="A395" s="1">
         <v>45820</v>
       </c>
       <c r="B395" t="s">
@@ -13810,7 +13816,7 @@
       </c>
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A396" s="2">
+      <c r="A396" s="1">
         <v>45821</v>
       </c>
       <c r="B396" t="s">
@@ -13830,7 +13836,7 @@
       </c>
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A397" s="2">
+      <c r="A397" s="1">
         <v>45821</v>
       </c>
       <c r="B397" t="s">
@@ -13850,7 +13856,7 @@
       </c>
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A398" s="2">
+      <c r="A398" s="1">
         <v>45824</v>
       </c>
       <c r="B398" t="s">
@@ -13870,7 +13876,7 @@
       </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A399" s="2">
+      <c r="A399" s="1">
         <v>45824</v>
       </c>
       <c r="B399" t="s">
@@ -13890,7 +13896,7 @@
       </c>
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A400" s="2">
+      <c r="A400" s="1">
         <v>45824</v>
       </c>
       <c r="B400" t="s">
@@ -13910,7 +13916,7 @@
       </c>
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A401" s="2">
+      <c r="A401" s="1">
         <v>45824</v>
       </c>
       <c r="B401" t="s">
@@ -13930,7 +13936,7 @@
       </c>
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A402" s="2">
+      <c r="A402" s="1">
         <v>45824</v>
       </c>
       <c r="B402" t="s">
@@ -13950,7 +13956,7 @@
       </c>
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A403" s="2">
+      <c r="A403" s="1">
         <v>45825</v>
       </c>
       <c r="B403" t="s">
@@ -13970,7 +13976,7 @@
       </c>
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A404" s="2">
+      <c r="A404" s="1">
         <v>45825</v>
       </c>
       <c r="B404" t="s">
@@ -13990,7 +13996,7 @@
       </c>
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A405" s="2">
+      <c r="A405" s="1">
         <v>45825</v>
       </c>
       <c r="B405" t="s">
@@ -14010,7 +14016,7 @@
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A406" s="2">
+      <c r="A406" s="1">
         <v>45825</v>
       </c>
       <c r="B406" t="s">
@@ -14030,7 +14036,7 @@
       </c>
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A407" s="2">
+      <c r="A407" s="1">
         <v>45828</v>
       </c>
       <c r="B407" t="s">
@@ -14050,7 +14056,7 @@
       </c>
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A408" s="2">
+      <c r="A408" s="1">
         <v>45828</v>
       </c>
       <c r="B408" t="s">
@@ -14070,7 +14076,7 @@
       </c>
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A409" s="2">
+      <c r="A409" s="1">
         <v>45828</v>
       </c>
       <c r="B409" t="s">
@@ -14090,7 +14096,7 @@
       </c>
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A410" s="2">
+      <c r="A410" s="1">
         <v>45828</v>
       </c>
       <c r="B410" t="s">
@@ -14110,7 +14116,7 @@
       </c>
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A411" s="2">
+      <c r="A411" s="1">
         <v>45834</v>
       </c>
       <c r="B411" t="s">
@@ -14130,7 +14136,7 @@
       </c>
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A412" s="2">
+      <c r="A412" s="1">
         <v>45838</v>
       </c>
       <c r="B412" t="s">
@@ -14150,7 +14156,7 @@
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A413" s="2">
+      <c r="A413" s="1">
         <v>45838</v>
       </c>
       <c r="B413" t="s">
@@ -14170,7 +14176,7 @@
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A414" s="2">
+      <c r="A414" s="1">
         <v>45839</v>
       </c>
       <c r="B414" t="s">
@@ -14190,7 +14196,7 @@
       </c>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A415" s="2">
+      <c r="A415" s="1">
         <v>45839</v>
       </c>
       <c r="B415" t="s">
@@ -14210,7 +14216,7 @@
       </c>
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A416" s="2">
+      <c r="A416" s="1">
         <v>45840</v>
       </c>
       <c r="B416" t="s">
@@ -14230,7 +14236,7 @@
       </c>
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A417" s="2">
+      <c r="A417" s="1">
         <v>45840</v>
       </c>
       <c r="B417" t="s">
@@ -14250,7 +14256,7 @@
       </c>
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A418" s="2">
+      <c r="A418" s="1">
         <v>45840</v>
       </c>
       <c r="B418" t="s">
@@ -14270,7 +14276,7 @@
       </c>
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A419" s="2">
+      <c r="A419" s="1">
         <v>45840</v>
       </c>
       <c r="B419" t="s">
@@ -14290,7 +14296,7 @@
       </c>
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A420" s="2">
+      <c r="A420" s="1">
         <v>45841</v>
       </c>
       <c r="B420" t="s">
@@ -14310,7 +14316,7 @@
       </c>
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A421" s="2">
+      <c r="A421" s="1">
         <v>45842</v>
       </c>
       <c r="B421" t="s">
@@ -14330,7 +14336,7 @@
       </c>
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A422" s="2">
+      <c r="A422" s="1">
         <v>45842</v>
       </c>
       <c r="B422" t="s">
@@ -14350,7 +14356,7 @@
       </c>
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A423" s="2">
+      <c r="A423" s="1">
         <v>45845</v>
       </c>
       <c r="B423" t="s">
@@ -14370,7 +14376,7 @@
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A424" s="2">
+      <c r="A424" s="1">
         <v>45845</v>
       </c>
       <c r="B424" t="s">
@@ -14390,7 +14396,7 @@
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A425" s="2">
+      <c r="A425" s="1">
         <v>45846</v>
       </c>
       <c r="B425" t="s">
@@ -14410,7 +14416,7 @@
       </c>
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A426" s="2">
+      <c r="A426" s="1">
         <v>45846</v>
       </c>
       <c r="B426" t="s">
@@ -14430,7 +14436,7 @@
       </c>
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A427" s="2">
+      <c r="A427" s="1">
         <v>45846</v>
       </c>
       <c r="B427" t="s">
@@ -14450,7 +14456,7 @@
       </c>
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A428" s="2">
+      <c r="A428" s="1">
         <v>45847</v>
       </c>
       <c r="B428" t="s">
@@ -14470,7 +14476,7 @@
       </c>
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A429" s="2">
+      <c r="A429" s="1">
         <v>45848</v>
       </c>
       <c r="B429" t="s">
@@ -14490,7 +14496,7 @@
       </c>
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A430" s="2">
+      <c r="A430" s="1">
         <v>45849</v>
       </c>
       <c r="B430" t="s">
@@ -14510,7 +14516,7 @@
       </c>
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A431" s="2">
+      <c r="A431" s="1">
         <v>45849</v>
       </c>
       <c r="B431" t="s">
@@ -14530,7 +14536,7 @@
       </c>
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A432" s="2">
+      <c r="A432" s="1">
         <v>45849</v>
       </c>
       <c r="B432" t="s">
@@ -14550,7 +14556,7 @@
       </c>
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A433" s="2">
+      <c r="A433" s="1">
         <v>45852</v>
       </c>
       <c r="B433" t="s">
@@ -14570,7 +14576,7 @@
       </c>
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A434" s="2">
+      <c r="A434" s="1">
         <v>45852</v>
       </c>
       <c r="B434" t="s">
@@ -14590,7 +14596,7 @@
       </c>
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A435" s="2">
+      <c r="A435" s="1">
         <v>45852</v>
       </c>
       <c r="B435" t="s">
@@ -14610,7 +14616,7 @@
       </c>
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A436" s="2">
+      <c r="A436" s="1">
         <v>45853</v>
       </c>
       <c r="B436" t="s">
@@ -14630,7 +14636,7 @@
       </c>
     </row>
     <row r="437" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A437" s="2">
+      <c r="A437" s="1">
         <v>45853</v>
       </c>
       <c r="B437" t="s">
@@ -14650,7 +14656,7 @@
       </c>
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A438" s="2">
+      <c r="A438" s="1">
         <v>45853</v>
       </c>
       <c r="B438" t="s">
@@ -14670,7 +14676,7 @@
       </c>
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A439" s="2">
+      <c r="A439" s="1">
         <v>45854</v>
       </c>
       <c r="B439" t="s">
@@ -14690,7 +14696,7 @@
       </c>
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A440" s="2">
+      <c r="A440" s="1">
         <v>45854</v>
       </c>
       <c r="B440" t="s">
@@ -14710,7 +14716,7 @@
       </c>
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A441" s="2">
+      <c r="A441" s="1">
         <v>45855</v>
       </c>
       <c r="B441" t="s">
@@ -14730,7 +14736,7 @@
       </c>
     </row>
     <row r="442" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A442" s="2">
+      <c r="A442" s="1">
         <v>45855</v>
       </c>
       <c r="B442" t="s">
@@ -14750,7 +14756,7 @@
       </c>
     </row>
     <row r="443" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A443" s="2">
+      <c r="A443" s="1">
         <v>45855</v>
       </c>
       <c r="B443" t="s">
@@ -14770,7 +14776,7 @@
       </c>
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A444" s="2">
+      <c r="A444" s="1">
         <v>45855</v>
       </c>
       <c r="B444" t="s">
@@ -14790,7 +14796,7 @@
       </c>
     </row>
     <row r="445" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A445" s="2">
+      <c r="A445" s="1">
         <v>45856</v>
       </c>
       <c r="B445" t="s">
@@ -14810,7 +14816,7 @@
       </c>
     </row>
     <row r="446" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A446" s="2">
+      <c r="A446" s="1">
         <v>45856</v>
       </c>
       <c r="B446" t="s">
@@ -14830,7 +14836,7 @@
       </c>
     </row>
     <row r="447" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A447" s="2">
+      <c r="A447" s="1">
         <v>45856</v>
       </c>
       <c r="B447" t="s">
@@ -14850,7 +14856,7 @@
       </c>
     </row>
     <row r="448" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A448" s="2">
+      <c r="A448" s="1">
         <v>45859</v>
       </c>
       <c r="B448" t="s">
@@ -14870,7 +14876,7 @@
       </c>
     </row>
     <row r="449" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A449" s="2">
+      <c r="A449" s="1">
         <v>45860</v>
       </c>
       <c r="B449" t="s">
@@ -14890,7 +14896,7 @@
       </c>
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A450" s="2">
+      <c r="A450" s="1">
         <v>45869</v>
       </c>
       <c r="B450" t="s">
@@ -14910,7 +14916,7 @@
       </c>
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A451" s="2">
+      <c r="A451" s="1">
         <v>45869</v>
       </c>
       <c r="B451" t="s">
@@ -14930,7 +14936,7 @@
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A452" s="2">
+      <c r="A452" s="1">
         <v>45870</v>
       </c>
       <c r="B452" t="s">
@@ -14950,7 +14956,7 @@
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A453" s="2">
+      <c r="A453" s="1">
         <v>45870</v>
       </c>
       <c r="B453" t="s">
@@ -14970,7 +14976,7 @@
       </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A454" s="2">
+      <c r="A454" s="1">
         <v>45870</v>
       </c>
       <c r="B454" t="s">
@@ -14990,7 +14996,7 @@
       </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A455" s="2">
+      <c r="A455" s="1">
         <v>45870</v>
       </c>
       <c r="B455" t="s">
@@ -15010,7 +15016,7 @@
       </c>
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A456" s="2">
+      <c r="A456" s="1">
         <v>45870</v>
       </c>
       <c r="B456" t="s">
@@ -15030,7 +15036,7 @@
       </c>
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A457" s="2">
+      <c r="A457" s="1">
         <v>45870</v>
       </c>
       <c r="B457" t="s">
@@ -15050,7 +15056,7 @@
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A458" s="2">
+      <c r="A458" s="1">
         <v>45873</v>
       </c>
       <c r="B458" t="s">
@@ -15070,7 +15076,7 @@
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A459" s="2">
+      <c r="A459" s="1">
         <v>45873</v>
       </c>
       <c r="B459" t="s">
@@ -15090,7 +15096,7 @@
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A460" s="2">
+      <c r="A460" s="1">
         <v>45873</v>
       </c>
       <c r="B460" t="s">
@@ -15110,7 +15116,7 @@
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A461" s="2">
+      <c r="A461" s="1">
         <v>45874</v>
       </c>
       <c r="B461" t="s">
@@ -15130,7 +15136,7 @@
       </c>
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A462" s="2">
+      <c r="A462" s="1">
         <v>45874</v>
       </c>
       <c r="B462" t="s">
@@ -15150,7 +15156,7 @@
       </c>
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A463" s="2">
+      <c r="A463" s="1">
         <v>45874</v>
       </c>
       <c r="B463" t="s">
@@ -15170,7 +15176,7 @@
       </c>
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A464" s="2">
+      <c r="A464" s="1">
         <v>45874</v>
       </c>
       <c r="B464" t="s">
@@ -15190,7 +15196,7 @@
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A465" s="2">
+      <c r="A465" s="1">
         <v>45874</v>
       </c>
       <c r="B465" t="s">
@@ -15210,7 +15216,7 @@
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A466" s="2">
+      <c r="A466" s="1">
         <v>45874</v>
       </c>
       <c r="B466" t="s">
@@ -15230,7 +15236,7 @@
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A467" s="2">
+      <c r="A467" s="1">
         <v>45874</v>
       </c>
       <c r="B467" t="s">
@@ -15250,7 +15256,7 @@
       </c>
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A468" s="2">
+      <c r="A468" s="1">
         <v>45875</v>
       </c>
       <c r="B468" t="s">
@@ -15270,7 +15276,7 @@
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A469" s="2">
+      <c r="A469" s="1">
         <v>45880</v>
       </c>
       <c r="B469" t="s">
@@ -15290,7 +15296,7 @@
       </c>
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A470" s="2">
+      <c r="A470" s="1">
         <v>45880</v>
       </c>
       <c r="B470" t="s">
@@ -15310,7 +15316,7 @@
       </c>
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A471" s="2">
+      <c r="A471" s="1">
         <v>45880</v>
       </c>
       <c r="B471" t="s">
@@ -15330,7 +15336,7 @@
       </c>
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A472" s="2">
+      <c r="A472" s="1">
         <v>45880</v>
       </c>
       <c r="B472" t="s">
@@ -15350,7 +15356,7 @@
       </c>
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A473" s="2">
+      <c r="A473" s="1">
         <v>45880</v>
       </c>
       <c r="B473" t="s">
@@ -15370,7 +15376,7 @@
       </c>
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A474" s="2">
+      <c r="A474" s="1">
         <v>45880</v>
       </c>
       <c r="B474" t="s">
@@ -15390,7 +15396,7 @@
       </c>
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A475" s="2">
+      <c r="A475" s="1">
         <v>45881</v>
       </c>
       <c r="B475" t="s">
@@ -15410,7 +15416,7 @@
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A476" s="2">
+      <c r="A476" s="1">
         <v>45881</v>
       </c>
       <c r="B476" t="s">
@@ -15430,7 +15436,7 @@
       </c>
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A477" s="2">
+      <c r="A477" s="1">
         <v>45882</v>
       </c>
       <c r="B477" t="s">
@@ -15450,7 +15456,7 @@
       </c>
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A478" s="2">
+      <c r="A478" s="1">
         <v>45882</v>
       </c>
       <c r="B478" t="s">
@@ -15470,7 +15476,7 @@
       </c>
     </row>
     <row r="479" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A479" s="2">
+      <c r="A479" s="1">
         <v>45882</v>
       </c>
       <c r="B479" t="s">
@@ -15490,7 +15496,7 @@
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A480" s="2">
+      <c r="A480" s="1">
         <v>45883</v>
       </c>
       <c r="B480" t="s">
@@ -15510,7 +15516,7 @@
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A481" s="2">
+      <c r="A481" s="1">
         <v>45883</v>
       </c>
       <c r="B481" t="s">
@@ -15530,7 +15536,7 @@
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A482" s="2">
+      <c r="A482" s="1">
         <v>45883</v>
       </c>
       <c r="B482" t="s">
@@ -15550,7 +15556,7 @@
       </c>
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A483" s="2">
+      <c r="A483" s="1">
         <v>45883</v>
       </c>
       <c r="B483" t="s">
@@ -15570,7 +15576,7 @@
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A484" s="2">
+      <c r="A484" s="1">
         <v>45884</v>
       </c>
       <c r="B484" t="s">
@@ -15590,7 +15596,7 @@
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A485" s="2">
+      <c r="A485" s="1">
         <v>45884</v>
       </c>
       <c r="B485" t="s">
@@ -15610,7 +15616,7 @@
       </c>
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A486" s="2">
+      <c r="A486" s="1">
         <v>45884</v>
       </c>
       <c r="B486" t="s">
@@ -15630,7 +15636,7 @@
       </c>
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A487" s="2">
+      <c r="A487" s="1">
         <v>45887</v>
       </c>
       <c r="B487" t="s">
@@ -15650,7 +15656,7 @@
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A488" s="2">
+      <c r="A488" s="1">
         <v>45888</v>
       </c>
       <c r="B488" t="s">
@@ -15670,7 +15676,7 @@
       </c>
     </row>
     <row r="489" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A489" s="2">
+      <c r="A489" s="1">
         <v>45890</v>
       </c>
       <c r="B489" t="s">
@@ -15690,7 +15696,7 @@
       </c>
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A490" s="2">
+      <c r="A490" s="1">
         <v>45890</v>
       </c>
       <c r="B490" t="s">
@@ -15710,7 +15716,7 @@
       </c>
     </row>
     <row r="491" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A491" s="2">
+      <c r="A491" s="1">
         <v>45891</v>
       </c>
       <c r="B491" t="s">
@@ -15730,7 +15736,7 @@
       </c>
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A492" s="2">
+      <c r="A492" s="1">
         <v>45894</v>
       </c>
       <c r="B492" t="s">
@@ -15750,7 +15756,7 @@
       </c>
     </row>
     <row r="493" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A493" s="2">
+      <c r="A493" s="1">
         <v>45895</v>
       </c>
       <c r="B493" t="s">
@@ -15770,7 +15776,7 @@
       </c>
     </row>
     <row r="494" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A494" s="2">
+      <c r="A494" s="1">
         <v>45895</v>
       </c>
       <c r="B494" t="s">
@@ -15790,7 +15796,7 @@
       </c>
     </row>
     <row r="495" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A495" s="2">
+      <c r="A495" s="1">
         <v>45896</v>
       </c>
       <c r="B495" t="s">
@@ -15810,7 +15816,7 @@
       </c>
     </row>
     <row r="496" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A496" s="2">
+      <c r="A496" s="1">
         <v>45896</v>
       </c>
       <c r="B496" t="s">
@@ -15830,7 +15836,7 @@
       </c>
     </row>
     <row r="497" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A497" s="2">
+      <c r="A497" s="1">
         <v>45898</v>
       </c>
       <c r="B497" t="s">
@@ -15850,7 +15856,7 @@
       </c>
     </row>
     <row r="498" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A498" s="2">
+      <c r="A498" s="1">
         <v>45898</v>
       </c>
       <c r="B498" t="s">
@@ -15870,7 +15876,7 @@
       </c>
     </row>
     <row r="499" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A499" s="2">
+      <c r="A499" s="1">
         <v>45898</v>
       </c>
       <c r="B499" t="s">
@@ -15890,7 +15896,7 @@
       </c>
     </row>
     <row r="500" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A500" s="2">
+      <c r="A500" s="1">
         <v>45898</v>
       </c>
       <c r="B500" t="s">
@@ -15910,7 +15916,7 @@
       </c>
     </row>
     <row r="501" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A501" s="2">
+      <c r="A501" s="1">
         <v>45899</v>
       </c>
       <c r="B501" t="s">
@@ -15930,7 +15936,7 @@
       </c>
     </row>
     <row r="502" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A502" s="2">
+      <c r="A502" s="1">
         <v>45901</v>
       </c>
       <c r="B502" t="s">
@@ -15950,7 +15956,7 @@
       </c>
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A503" s="2">
+      <c r="A503" s="1">
         <v>45901</v>
       </c>
       <c r="B503" t="s">
@@ -15970,7 +15976,7 @@
       </c>
     </row>
     <row r="504" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A504" s="2">
+      <c r="A504" s="1">
         <v>45902</v>
       </c>
       <c r="B504" t="s">
@@ -15990,7 +15996,7 @@
       </c>
     </row>
     <row r="505" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A505" s="2">
+      <c r="A505" s="1">
         <v>45902</v>
       </c>
       <c r="B505" t="s">
@@ -16010,7 +16016,7 @@
       </c>
     </row>
     <row r="506" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A506" s="2">
+      <c r="A506" s="1">
         <v>45904</v>
       </c>
       <c r="B506" t="s">
@@ -16030,7 +16036,7 @@
       </c>
     </row>
     <row r="507" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A507" s="2">
+      <c r="A507" s="1">
         <v>45904</v>
       </c>
       <c r="B507" t="s">
@@ -16050,7 +16056,7 @@
       </c>
     </row>
     <row r="508" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A508" s="2">
+      <c r="A508" s="1">
         <v>45904</v>
       </c>
       <c r="B508" t="s">
@@ -16070,7 +16076,7 @@
       </c>
     </row>
     <row r="509" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A509" s="2">
+      <c r="A509" s="1">
         <v>45904</v>
       </c>
       <c r="B509" t="s">
@@ -16090,7 +16096,7 @@
       </c>
     </row>
     <row r="510" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A510" s="2">
+      <c r="A510" s="1">
         <v>45904</v>
       </c>
       <c r="B510" t="s">
@@ -16110,7 +16116,7 @@
       </c>
     </row>
     <row r="511" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A511" s="2">
+      <c r="A511" s="1">
         <v>45904</v>
       </c>
       <c r="B511" t="s">
@@ -16130,7 +16136,7 @@
       </c>
     </row>
     <row r="512" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A512" s="2">
+      <c r="A512" s="1">
         <v>45904</v>
       </c>
       <c r="B512" t="s">
@@ -16150,7 +16156,7 @@
       </c>
     </row>
     <row r="513" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A513" s="2">
+      <c r="A513" s="1">
         <v>45904</v>
       </c>
       <c r="B513" t="s">
@@ -16170,7 +16176,7 @@
       </c>
     </row>
     <row r="514" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A514" s="2">
+      <c r="A514" s="1">
         <v>45904</v>
       </c>
       <c r="B514" t="s">
@@ -16190,7 +16196,7 @@
       </c>
     </row>
     <row r="515" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A515" s="2">
+      <c r="A515" s="1">
         <v>45904</v>
       </c>
       <c r="B515" t="s">
@@ -16210,7 +16216,7 @@
       </c>
     </row>
     <row r="516" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A516" s="2">
+      <c r="A516" s="1">
         <v>45905</v>
       </c>
       <c r="B516" t="s">
@@ -16230,7 +16236,7 @@
       </c>
     </row>
     <row r="517" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A517" s="2">
+      <c r="A517" s="1">
         <v>45905</v>
       </c>
       <c r="B517" t="s">
@@ -16250,7 +16256,7 @@
       </c>
     </row>
     <row r="518" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A518" s="2">
+      <c r="A518" s="1">
         <v>45905</v>
       </c>
       <c r="B518" t="s">
@@ -16270,7 +16276,7 @@
       </c>
     </row>
     <row r="519" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A519" s="2">
+      <c r="A519" s="1">
         <v>45905</v>
       </c>
       <c r="B519" t="s">
@@ -16290,7 +16296,7 @@
       </c>
     </row>
     <row r="520" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A520" s="2">
+      <c r="A520" s="1">
         <v>45908</v>
       </c>
       <c r="B520" t="s">
@@ -16310,7 +16316,7 @@
       </c>
     </row>
     <row r="521" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A521" s="2">
+      <c r="A521" s="1">
         <v>45908</v>
       </c>
       <c r="B521" t="s">
@@ -16330,7 +16336,7 @@
       </c>
     </row>
     <row r="522" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A522" s="2">
+      <c r="A522" s="1">
         <v>45908</v>
       </c>
       <c r="B522" t="s">
@@ -16350,7 +16356,7 @@
       </c>
     </row>
     <row r="523" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A523" s="2">
+      <c r="A523" s="1">
         <v>45911</v>
       </c>
       <c r="B523" t="s">
@@ -16370,7 +16376,7 @@
       </c>
     </row>
     <row r="524" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A524" s="2">
+      <c r="A524" s="1">
         <v>45912</v>
       </c>
       <c r="B524" t="s">
@@ -16390,7 +16396,7 @@
       </c>
     </row>
     <row r="525" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A525" s="2">
+      <c r="A525" s="1">
         <v>45912</v>
       </c>
       <c r="B525" t="s">
@@ -16410,7 +16416,7 @@
       </c>
     </row>
     <row r="526" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A526" s="2">
+      <c r="A526" s="1">
         <v>45912</v>
       </c>
       <c r="B526" t="s">
@@ -16430,7 +16436,7 @@
       </c>
     </row>
     <row r="527" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A527" s="2">
+      <c r="A527" s="1">
         <v>45912</v>
       </c>
       <c r="B527" t="s">
@@ -16450,7 +16456,7 @@
       </c>
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A528" s="2">
+      <c r="A528" s="1">
         <v>45915</v>
       </c>
       <c r="B528" t="s">
@@ -16470,7 +16476,7 @@
       </c>
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A529" s="2">
+      <c r="A529" s="1">
         <v>45915</v>
       </c>
       <c r="B529" t="s">
@@ -16490,7 +16496,7 @@
       </c>
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A530" s="2">
+      <c r="A530" s="1">
         <v>45915</v>
       </c>
       <c r="B530" t="s">
@@ -16510,7 +16516,7 @@
       </c>
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A531" s="2">
+      <c r="A531" s="1">
         <v>45916</v>
       </c>
       <c r="B531" t="s">
@@ -16530,7 +16536,7 @@
       </c>
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A532" s="2">
+      <c r="A532" s="1">
         <v>45916</v>
       </c>
       <c r="B532" t="s">
@@ -16550,7 +16556,7 @@
       </c>
     </row>
     <row r="533" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A533" s="2">
+      <c r="A533" s="1">
         <v>45916</v>
       </c>
       <c r="B533" t="s">
@@ -16570,7 +16576,7 @@
       </c>
     </row>
     <row r="534" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A534" s="2">
+      <c r="A534" s="1">
         <v>45916</v>
       </c>
       <c r="B534" t="s">
@@ -16590,7 +16596,7 @@
       </c>
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A535" s="2">
+      <c r="A535" s="1">
         <v>45917</v>
       </c>
       <c r="B535" t="s">
@@ -16610,7 +16616,7 @@
       </c>
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A536" s="2">
+      <c r="A536" s="1">
         <v>45923</v>
       </c>
       <c r="B536" t="s">
@@ -16630,7 +16636,7 @@
       </c>
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A537" s="2">
+      <c r="A537" s="1">
         <v>45923</v>
       </c>
       <c r="B537" t="s">
@@ -16650,7 +16656,7 @@
       </c>
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A538" s="2">
+      <c r="A538" s="1">
         <v>45923</v>
       </c>
       <c r="B538" t="s">
@@ -16670,7 +16676,7 @@
       </c>
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A539" s="2">
+      <c r="A539" s="1">
         <v>45923</v>
       </c>
       <c r="B539" t="s">
@@ -16690,7 +16696,7 @@
       </c>
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A540" s="2">
+      <c r="A540" s="1">
         <v>45925</v>
       </c>
       <c r="B540" t="s">
@@ -16710,7 +16716,7 @@
       </c>
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A541" s="2">
+      <c r="A541" s="1">
         <v>45926</v>
       </c>
       <c r="B541" t="s">
@@ -16730,7 +16736,7 @@
       </c>
     </row>
     <row r="542" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A542" s="2">
+      <c r="A542" s="1">
         <v>45926</v>
       </c>
       <c r="B542" t="s">
@@ -16750,7 +16756,7 @@
       </c>
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A543" s="2">
+      <c r="A543" s="1">
         <v>45929</v>
       </c>
       <c r="B543" t="s">
@@ -16770,7 +16776,7 @@
       </c>
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A544" s="2">
+      <c r="A544" s="1">
         <v>45930</v>
       </c>
       <c r="B544" t="s">
@@ -16790,7 +16796,7 @@
       </c>
     </row>
     <row r="545" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A545" s="2">
+      <c r="A545" s="1">
         <v>45930</v>
       </c>
       <c r="B545" t="s">
@@ -16810,7 +16816,7 @@
       </c>
     </row>
     <row r="546" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A546" s="2">
+      <c r="A546" s="1">
         <v>45930</v>
       </c>
       <c r="B546" t="s">
@@ -16830,7 +16836,7 @@
       </c>
     </row>
     <row r="547" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A547" s="2">
+      <c r="A547" s="1">
         <v>45931</v>
       </c>
       <c r="B547" t="s">
@@ -16850,7 +16856,7 @@
       </c>
     </row>
     <row r="548" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A548" s="2">
+      <c r="A548" s="1">
         <v>45931</v>
       </c>
       <c r="B548" t="s">
@@ -16870,7 +16876,7 @@
       </c>
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A549" s="2">
+      <c r="A549" s="1">
         <v>45931</v>
       </c>
       <c r="B549" t="s">
@@ -16890,7 +16896,7 @@
       </c>
     </row>
     <row r="550" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A550" s="2">
+      <c r="A550" s="1">
         <v>45931</v>
       </c>
       <c r="B550" t="s">
@@ -16910,7 +16916,7 @@
       </c>
     </row>
     <row r="551" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A551" s="2">
+      <c r="A551" s="1">
         <v>45933</v>
       </c>
       <c r="B551" t="s">
@@ -16930,7 +16936,7 @@
       </c>
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A552" s="2">
+      <c r="A552" s="1">
         <v>45933</v>
       </c>
       <c r="B552" t="s">
@@ -16950,7 +16956,7 @@
       </c>
     </row>
     <row r="553" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A553" s="2">
+      <c r="A553" s="1">
         <v>45937</v>
       </c>
       <c r="B553" t="s">
@@ -16970,7 +16976,7 @@
       </c>
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A554" s="2">
+      <c r="A554" s="1">
         <v>45937</v>
       </c>
       <c r="B554" t="s">
@@ -16990,7 +16996,7 @@
       </c>
     </row>
     <row r="555" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A555" s="2">
+      <c r="A555" s="1">
         <v>45937</v>
       </c>
       <c r="B555" t="s">
@@ -17010,7 +17016,7 @@
       </c>
     </row>
     <row r="556" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A556" s="2">
+      <c r="A556" s="1">
         <v>45939</v>
       </c>
       <c r="B556" t="s">
@@ -17030,7 +17036,7 @@
       </c>
     </row>
     <row r="557" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A557" s="2">
+      <c r="A557" s="1">
         <v>45940</v>
       </c>
       <c r="B557" t="s">
@@ -17050,7 +17056,7 @@
       </c>
     </row>
     <row r="558" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A558" s="2">
+      <c r="A558" s="1">
         <v>45940</v>
       </c>
       <c r="B558" t="s">
@@ -17070,7 +17076,7 @@
       </c>
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A559" s="2">
+      <c r="A559" s="1">
         <v>45943</v>
       </c>
       <c r="B559" t="s">
@@ -17090,7 +17096,7 @@
       </c>
     </row>
     <row r="560" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A560" s="2">
+      <c r="A560" s="1">
         <v>45943</v>
       </c>
       <c r="B560" t="s">
@@ -17110,7 +17116,7 @@
       </c>
     </row>
     <row r="561" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A561" s="2">
+      <c r="A561" s="1">
         <v>45943</v>
       </c>
       <c r="B561" t="s">
@@ -17130,7 +17136,7 @@
       </c>
     </row>
     <row r="562" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A562" s="2">
+      <c r="A562" s="1">
         <v>45943</v>
       </c>
       <c r="B562" t="s">
@@ -17150,7 +17156,7 @@
       </c>
     </row>
     <row r="563" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A563" s="2">
+      <c r="A563" s="1">
         <v>45945</v>
       </c>
       <c r="B563" t="s">
@@ -17170,7 +17176,7 @@
       </c>
     </row>
     <row r="564" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A564" s="2">
+      <c r="A564" s="1">
         <v>45945</v>
       </c>
       <c r="B564" t="s">
@@ -17190,7 +17196,7 @@
       </c>
     </row>
     <row r="565" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A565" s="2">
+      <c r="A565" s="1">
         <v>45950</v>
       </c>
       <c r="B565" t="s">
@@ -17210,7 +17216,7 @@
       </c>
     </row>
     <row r="566" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A566" s="2">
+      <c r="A566" s="1">
         <v>45950</v>
       </c>
       <c r="B566" t="s">
@@ -17230,7 +17236,7 @@
       </c>
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A567" s="2">
+      <c r="A567" s="1">
         <v>45950</v>
       </c>
       <c r="B567" t="s">
@@ -17250,7 +17256,7 @@
       </c>
     </row>
     <row r="568" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A568" s="2">
+      <c r="A568" s="1">
         <v>45950</v>
       </c>
       <c r="B568" t="s">
@@ -17270,7 +17276,7 @@
       </c>
     </row>
     <row r="569" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A569" s="2">
+      <c r="A569" s="1">
         <v>45951</v>
       </c>
       <c r="B569" t="s">
@@ -17290,7 +17296,7 @@
       </c>
     </row>
     <row r="570" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A570" s="2">
+      <c r="A570" s="1">
         <v>45951</v>
       </c>
       <c r="B570" t="s">
@@ -17310,7 +17316,7 @@
       </c>
     </row>
     <row r="571" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A571" s="2">
+      <c r="A571" s="1">
         <v>45951</v>
       </c>
       <c r="B571" t="s">
@@ -17330,7 +17336,7 @@
       </c>
     </row>
     <row r="572" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A572" s="2">
+      <c r="A572" s="1">
         <v>45952</v>
       </c>
       <c r="B572" t="s">
@@ -17350,7 +17356,7 @@
       </c>
     </row>
     <row r="573" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A573" s="2">
+      <c r="A573" s="1">
         <v>45952</v>
       </c>
       <c r="B573" t="s">
@@ -17370,7 +17376,7 @@
       </c>
     </row>
     <row r="574" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A574" s="2">
+      <c r="A574" s="1">
         <v>45954</v>
       </c>
       <c r="B574" t="s">
@@ -17390,7 +17396,7 @@
       </c>
     </row>
     <row r="575" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A575" s="2">
+      <c r="A575" s="1">
         <v>45957</v>
       </c>
       <c r="B575" t="s">
@@ -17410,7 +17416,7 @@
       </c>
     </row>
     <row r="576" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A576" s="2">
+      <c r="A576" s="1">
         <v>45957</v>
       </c>
       <c r="B576" t="s">
@@ -17430,7 +17436,7 @@
       </c>
     </row>
     <row r="577" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A577" s="2">
+      <c r="A577" s="1">
         <v>45958</v>
       </c>
       <c r="B577" t="s">
@@ -17450,7 +17456,7 @@
       </c>
     </row>
     <row r="578" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A578" s="2">
+      <c r="A578" s="1">
         <v>45958</v>
       </c>
       <c r="B578" t="s">
@@ -17470,7 +17476,7 @@
       </c>
     </row>
     <row r="579" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A579" s="2">
+      <c r="A579" s="1">
         <v>45958</v>
       </c>
       <c r="B579" t="s">
@@ -17490,7 +17496,7 @@
       </c>
     </row>
     <row r="580" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A580" s="2">
+      <c r="A580" s="1">
         <v>45958</v>
       </c>
       <c r="B580" t="s">
@@ -17510,7 +17516,7 @@
       </c>
     </row>
     <row r="581" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A581" s="2">
+      <c r="A581" s="1">
         <v>45961</v>
       </c>
       <c r="B581" t="s">
@@ -17530,7 +17536,7 @@
       </c>
     </row>
     <row r="582" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A582" s="2">
+      <c r="A582" s="1">
         <v>45961</v>
       </c>
       <c r="B582" t="s">
@@ -17550,7 +17556,7 @@
       </c>
     </row>
     <row r="583" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A583" s="2">
+      <c r="A583" s="1">
         <v>45961</v>
       </c>
       <c r="B583" t="s">
@@ -17570,7 +17576,7 @@
       </c>
     </row>
     <row r="584" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A584" s="2">
+      <c r="A584" s="1">
         <v>45961</v>
       </c>
       <c r="B584" t="s">
@@ -17590,7 +17596,7 @@
       </c>
     </row>
     <row r="585" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A585" s="2">
+      <c r="A585" s="1">
         <v>45962</v>
       </c>
       <c r="B585" t="s">
@@ -17610,7 +17616,7 @@
       </c>
     </row>
     <row r="586" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A586" s="2">
+      <c r="A586" s="1">
         <v>45964</v>
       </c>
       <c r="B586" t="s">
@@ -17630,7 +17636,7 @@
       </c>
     </row>
     <row r="587" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A587" s="2">
+      <c r="A587" s="1">
         <v>45964</v>
       </c>
       <c r="B587" t="s">
@@ -17650,7 +17656,7 @@
       </c>
     </row>
     <row r="588" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A588" s="2">
+      <c r="A588" s="1">
         <v>45964</v>
       </c>
       <c r="B588" t="s">
@@ -17670,7 +17676,7 @@
       </c>
     </row>
     <row r="589" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A589" s="2">
+      <c r="A589" s="1">
         <v>45964</v>
       </c>
       <c r="B589" t="s">
@@ -17690,7 +17696,7 @@
       </c>
     </row>
     <row r="590" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A590" s="2">
+      <c r="A590" s="1">
         <v>45964</v>
       </c>
       <c r="B590" t="s">
@@ -17710,7 +17716,7 @@
       </c>
     </row>
     <row r="591" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A591" s="2">
+      <c r="A591" s="1">
         <v>45964</v>
       </c>
       <c r="B591" t="s">
@@ -17730,7 +17736,7 @@
       </c>
     </row>
     <row r="592" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A592" s="2">
+      <c r="A592" s="1">
         <v>45964</v>
       </c>
       <c r="B592" t="s">
@@ -17750,7 +17756,7 @@
       </c>
     </row>
     <row r="593" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A593" s="2">
+      <c r="A593" s="1">
         <v>45964</v>
       </c>
       <c r="B593" t="s">
@@ -17770,7 +17776,7 @@
       </c>
     </row>
     <row r="594" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A594" s="2">
+      <c r="A594" s="1">
         <v>45964</v>
       </c>
       <c r="B594" t="s">
@@ -17790,7 +17796,7 @@
       </c>
     </row>
     <row r="595" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A595" s="2">
+      <c r="A595" s="1">
         <v>45965</v>
       </c>
       <c r="B595" t="s">
@@ -17810,7 +17816,7 @@
       </c>
     </row>
     <row r="596" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A596" s="2">
+      <c r="A596" s="1">
         <v>45966</v>
       </c>
       <c r="B596" t="s">
@@ -17830,7 +17836,7 @@
       </c>
     </row>
     <row r="597" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A597" s="2">
+      <c r="A597" s="1">
         <v>45967</v>
       </c>
       <c r="B597" t="s">
@@ -17850,7 +17856,7 @@
       </c>
     </row>
     <row r="598" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A598" s="2">
+      <c r="A598" s="1">
         <v>45968</v>
       </c>
       <c r="B598" t="s">
@@ -17870,7 +17876,7 @@
       </c>
     </row>
     <row r="599" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A599" s="2">
+      <c r="A599" s="1">
         <v>45968</v>
       </c>
       <c r="B599" t="s">
@@ -17890,7 +17896,7 @@
       </c>
     </row>
     <row r="600" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A600" s="2">
+      <c r="A600" s="1">
         <v>45971</v>
       </c>
       <c r="B600" t="s">
@@ -17910,7 +17916,7 @@
       </c>
     </row>
     <row r="601" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A601" s="2">
+      <c r="A601" s="1">
         <v>45971</v>
       </c>
       <c r="B601" t="s">
@@ -17930,7 +17936,7 @@
       </c>
     </row>
     <row r="602" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A602" s="2">
+      <c r="A602" s="1">
         <v>45971</v>
       </c>
       <c r="B602" t="s">
@@ -17950,7 +17956,7 @@
       </c>
     </row>
     <row r="603" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A603" s="2">
+      <c r="A603" s="1">
         <v>45973</v>
       </c>
       <c r="B603" t="s">
@@ -17970,7 +17976,7 @@
       </c>
     </row>
     <row r="604" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A604" s="2">
+      <c r="A604" s="1">
         <v>45973</v>
       </c>
       <c r="B604" t="s">
@@ -17990,7 +17996,7 @@
       </c>
     </row>
     <row r="605" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A605" s="2">
+      <c r="A605" s="1">
         <v>45973</v>
       </c>
       <c r="B605" t="s">
@@ -18010,7 +18016,7 @@
       </c>
     </row>
     <row r="606" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A606" s="2">
+      <c r="A606" s="1">
         <v>45973</v>
       </c>
       <c r="B606" t="s">
@@ -18030,7 +18036,7 @@
       </c>
     </row>
     <row r="607" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A607" s="2">
+      <c r="A607" s="1">
         <v>45974</v>
       </c>
       <c r="B607" t="s">
@@ -18050,7 +18056,7 @@
       </c>
     </row>
     <row r="608" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A608" s="2">
+      <c r="A608" s="1">
         <v>45975</v>
       </c>
       <c r="B608" t="s">
@@ -18070,7 +18076,7 @@
       </c>
     </row>
     <row r="609" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A609" s="2">
+      <c r="A609" s="1">
         <v>45975</v>
       </c>
       <c r="B609" t="s">
@@ -18090,7 +18096,7 @@
       </c>
     </row>
     <row r="610" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A610" s="2">
+      <c r="A610" s="1">
         <v>45978</v>
       </c>
       <c r="B610" t="s">
@@ -18110,7 +18116,7 @@
       </c>
     </row>
     <row r="611" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A611" s="2">
+      <c r="A611" s="1">
         <v>45978</v>
       </c>
       <c r="B611" t="s">
@@ -18130,7 +18136,7 @@
       </c>
     </row>
     <row r="612" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A612" s="2">
+      <c r="A612" s="1">
         <v>45978</v>
       </c>
       <c r="B612" t="s">
@@ -18150,7 +18156,7 @@
       </c>
     </row>
     <row r="613" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A613" s="2">
+      <c r="A613" s="1">
         <v>45978</v>
       </c>
       <c r="B613" t="s">
@@ -18170,7 +18176,7 @@
       </c>
     </row>
     <row r="614" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A614" s="2">
+      <c r="A614" s="1">
         <v>45978</v>
       </c>
       <c r="B614" t="s">
@@ -18190,7 +18196,7 @@
       </c>
     </row>
     <row r="615" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A615" s="2">
+      <c r="A615" s="1">
         <v>45980</v>
       </c>
       <c r="B615" t="s">
@@ -18210,7 +18216,7 @@
       </c>
     </row>
     <row r="616" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A616" s="2">
+      <c r="A616" s="1">
         <v>45981</v>
       </c>
       <c r="B616" t="s">
@@ -18230,7 +18236,7 @@
       </c>
     </row>
     <row r="617" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A617" s="2">
+      <c r="A617" s="1">
         <v>45982</v>
       </c>
       <c r="B617" t="s">
@@ -18250,7 +18256,7 @@
       </c>
     </row>
     <row r="618" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A618" s="2">
+      <c r="A618" s="1">
         <v>45982</v>
       </c>
       <c r="B618" t="s">
@@ -18270,7 +18276,7 @@
       </c>
     </row>
     <row r="619" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A619" s="2">
+      <c r="A619" s="1">
         <v>45982</v>
       </c>
       <c r="B619" t="s">
@@ -18290,7 +18296,7 @@
       </c>
     </row>
     <row r="620" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A620" s="2">
+      <c r="A620" s="1">
         <v>45986</v>
       </c>
       <c r="B620" t="s">
@@ -18310,7 +18316,7 @@
       </c>
     </row>
     <row r="621" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A621" s="2">
+      <c r="A621" s="1">
         <v>45986</v>
       </c>
       <c r="B621" t="s">
@@ -18330,7 +18336,7 @@
       </c>
     </row>
     <row r="622" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A622" s="2">
+      <c r="A622" s="1">
         <v>45986</v>
       </c>
       <c r="B622" t="s">
@@ -18350,7 +18356,7 @@
       </c>
     </row>
     <row r="623" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A623" s="2">
+      <c r="A623" s="1">
         <v>45986</v>
       </c>
       <c r="B623" t="s">
@@ -18370,7 +18376,7 @@
       </c>
     </row>
     <row r="624" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A624" s="2">
+      <c r="A624" s="1">
         <v>45987</v>
       </c>
       <c r="B624" t="s">
@@ -18390,7 +18396,7 @@
       </c>
     </row>
     <row r="625" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A625" s="2">
+      <c r="A625" s="1">
         <v>45987</v>
       </c>
       <c r="B625" t="s">
@@ -18410,7 +18416,7 @@
       </c>
     </row>
     <row r="626" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A626" s="2">
+      <c r="A626" s="1">
         <v>45987</v>
       </c>
       <c r="B626" t="s">
@@ -18430,7 +18436,7 @@
       </c>
     </row>
     <row r="627" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A627" s="2">
+      <c r="A627" s="1">
         <v>45987</v>
       </c>
       <c r="B627" t="s">
@@ -18450,7 +18456,7 @@
       </c>
     </row>
     <row r="628" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A628" s="2">
+      <c r="A628" s="1">
         <v>45987</v>
       </c>
       <c r="B628" t="s">
@@ -18470,7 +18476,7 @@
       </c>
     </row>
     <row r="629" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A629" s="2">
+      <c r="A629" s="1">
         <v>45988</v>
       </c>
       <c r="B629" t="s">
@@ -18490,7 +18496,7 @@
       </c>
     </row>
     <row r="630" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A630" s="2">
+      <c r="A630" s="1">
         <v>45988</v>
       </c>
       <c r="B630" t="s">
@@ -18510,7 +18516,7 @@
       </c>
     </row>
     <row r="631" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A631" s="2">
+      <c r="A631" s="1">
         <v>45989</v>
       </c>
       <c r="B631" t="s">
@@ -18530,7 +18536,7 @@
       </c>
     </row>
     <row r="632" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A632" s="2">
+      <c r="A632" s="1">
         <v>45989</v>
       </c>
       <c r="B632" t="s">
@@ -18550,7 +18556,7 @@
       </c>
     </row>
     <row r="633" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A633" s="2">
+      <c r="A633" s="1">
         <v>45989</v>
       </c>
       <c r="B633" t="s">
@@ -18570,7 +18576,7 @@
       </c>
     </row>
     <row r="634" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A634" s="2">
+      <c r="A634" s="1">
         <v>45990</v>
       </c>
       <c r="B634" t="s">
@@ -18590,7 +18596,7 @@
       </c>
     </row>
     <row r="635" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A635" s="2">
+      <c r="A635" s="1">
         <v>45992</v>
       </c>
       <c r="B635" t="s">
@@ -18610,7 +18616,7 @@
       </c>
     </row>
     <row r="636" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A636" s="2">
+      <c r="A636" s="1">
         <v>45992</v>
       </c>
       <c r="B636" t="s">
@@ -18630,7 +18636,7 @@
       </c>
     </row>
     <row r="637" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A637" s="2">
+      <c r="A637" s="1">
         <v>45992</v>
       </c>
       <c r="B637" t="s">
@@ -18650,7 +18656,7 @@
       </c>
     </row>
     <row r="638" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A638" s="2">
+      <c r="A638" s="1">
         <v>45992</v>
       </c>
       <c r="B638" t="s">
@@ -18670,7 +18676,7 @@
       </c>
     </row>
     <row r="639" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A639" s="2">
+      <c r="A639" s="1">
         <v>45993</v>
       </c>
       <c r="B639" t="s">
@@ -18690,7 +18696,7 @@
       </c>
     </row>
     <row r="640" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A640" s="2">
+      <c r="A640" s="1">
         <v>45993</v>
       </c>
       <c r="B640" t="s">
@@ -18710,7 +18716,7 @@
       </c>
     </row>
     <row r="641" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A641" s="2">
+      <c r="A641" s="1">
         <v>45994</v>
       </c>
       <c r="B641" t="s">
@@ -18730,7 +18736,7 @@
       </c>
     </row>
     <row r="642" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A642" s="2">
+      <c r="A642" s="1">
         <v>45994</v>
       </c>
       <c r="B642" t="s">
@@ -18750,7 +18756,7 @@
       </c>
     </row>
     <row r="643" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A643" s="2">
+      <c r="A643" s="1">
         <v>45994</v>
       </c>
       <c r="B643" t="s">
@@ -18770,7 +18776,7 @@
       </c>
     </row>
     <row r="644" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A644" s="2">
+      <c r="A644" s="1">
         <v>45994</v>
       </c>
       <c r="B644" t="s">
@@ -18790,7 +18796,7 @@
       </c>
     </row>
     <row r="645" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A645" s="2">
+      <c r="A645" s="1">
         <v>45994</v>
       </c>
       <c r="B645" t="s">
@@ -18810,7 +18816,7 @@
       </c>
     </row>
     <row r="646" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A646" s="2">
+      <c r="A646" s="1">
         <v>46003</v>
       </c>
       <c r="B646" t="s">
@@ -18830,7 +18836,7 @@
       </c>
     </row>
     <row r="647" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A647" s="2">
+      <c r="A647" s="1">
         <v>46003</v>
       </c>
       <c r="B647" t="s">
@@ -18850,7 +18856,7 @@
       </c>
     </row>
     <row r="648" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A648" s="2">
+      <c r="A648" s="1">
         <v>46003</v>
       </c>
       <c r="B648" t="s">
@@ -18870,7 +18876,7 @@
       </c>
     </row>
     <row r="649" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A649" s="2">
+      <c r="A649" s="1">
         <v>46003</v>
       </c>
       <c r="B649" t="s">
@@ -18890,7 +18896,7 @@
       </c>
     </row>
     <row r="650" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A650" s="2">
+      <c r="A650" s="1">
         <v>46003</v>
       </c>
       <c r="B650" t="s">
@@ -18910,7 +18916,7 @@
       </c>
     </row>
     <row r="651" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A651" s="2">
+      <c r="A651" s="1">
         <v>46006</v>
       </c>
       <c r="B651" t="s">
@@ -18930,7 +18936,7 @@
       </c>
     </row>
     <row r="652" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A652" s="2">
+      <c r="A652" s="1">
         <v>46007</v>
       </c>
       <c r="B652" t="s">
@@ -18950,7 +18956,7 @@
       </c>
     </row>
     <row r="653" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A653" s="2">
+      <c r="A653" s="1">
         <v>46008</v>
       </c>
       <c r="B653" t="s">
@@ -18970,7 +18976,7 @@
       </c>
     </row>
     <row r="654" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A654" s="2">
+      <c r="A654" s="1">
         <v>46008</v>
       </c>
       <c r="B654" t="s">
@@ -18990,7 +18996,7 @@
       </c>
     </row>
     <row r="655" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A655" s="2">
+      <c r="A655" s="1">
         <v>46009</v>
       </c>
       <c r="B655" t="s">
@@ -19010,7 +19016,7 @@
       </c>
     </row>
     <row r="656" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A656" s="2">
+      <c r="A656" s="1">
         <v>46009</v>
       </c>
       <c r="B656" t="s">
@@ -19030,7 +19036,7 @@
       </c>
     </row>
     <row r="657" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A657" s="2">
+      <c r="A657" s="1">
         <v>46009</v>
       </c>
       <c r="B657" t="s">
@@ -19050,7 +19056,7 @@
       </c>
     </row>
     <row r="658" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A658" s="2">
+      <c r="A658" s="1">
         <v>46010</v>
       </c>
       <c r="B658" t="s">
@@ -19070,7 +19076,7 @@
       </c>
     </row>
     <row r="659" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A659" s="2">
+      <c r="A659" s="1">
         <v>46010</v>
       </c>
       <c r="B659" t="s">
@@ -19090,7 +19096,7 @@
       </c>
     </row>
     <row r="660" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A660" s="2">
+      <c r="A660" s="1">
         <v>46010</v>
       </c>
       <c r="B660" t="s">
@@ -19110,7 +19116,7 @@
       </c>
     </row>
     <row r="661" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A661" s="2">
+      <c r="A661" s="1">
         <v>46017</v>
       </c>
       <c r="B661" t="s">
@@ -19130,7 +19136,7 @@
       </c>
     </row>
     <row r="662" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A662" s="2">
+      <c r="A662" s="1">
         <v>46020</v>
       </c>
       <c r="B662" t="s">
@@ -19150,7 +19156,7 @@
       </c>
     </row>
     <row r="663" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A663" s="2">
+      <c r="A663" s="1">
         <v>46021</v>
       </c>
       <c r="B663" t="s">
@@ -19170,7 +19176,7 @@
       </c>
     </row>
     <row r="664" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A664" s="2">
+      <c r="A664" s="1">
         <v>46022</v>
       </c>
       <c r="B664" t="s">
@@ -19190,7 +19196,7 @@
       </c>
     </row>
     <row r="665" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A665" s="2">
+      <c r="A665" s="1">
         <v>46022</v>
       </c>
       <c r="B665" t="s">
@@ -19210,7 +19216,7 @@
       </c>
     </row>
     <row r="666" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A666" s="2">
+      <c r="A666" s="1">
         <v>46022</v>
       </c>
       <c r="B666" t="s">
